--- a/dummy-content/MARJANE-MALL-EXPORT-DATA.xlsx
+++ b/dummy-content/MARJANE-MALL-EXPORT-DATA.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UNK\Desktop\GoFleet-Enhancer\dummy-content\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A857A25-44AB-4BB4-9A6F-B0274CEB4FA4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B429A02-3AE0-457C-8943-853C184D8995}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -45,9 +45,6 @@
     <t>Non Livrés</t>
   </si>
   <si>
-    <t>R.Livré</t>
-  </si>
-  <si>
     <t>R.Récupéré</t>
   </si>
   <si>
@@ -56,12 +53,18 @@
   <si>
     <t>T.Colis</t>
   </si>
+  <si>
+    <t>R.Ajourné</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,6 +81,13 @@
     </font>
     <font>
       <sz val="16"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -180,14 +190,30 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -195,12 +221,80 @@
   </cellStyles>
   <dxfs count="12">
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor rgb="FFAEFEFC"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -217,32 +311,25 @@
       </border>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor theme="9" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -259,12 +346,25 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.59999389629810485"/>
+          <bgColor theme="3" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -281,12 +381,25 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor rgb="FFFFAFAF"/>
+          <bgColor theme="3" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -303,12 +416,25 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor theme="8" tint="0.79998168889431442"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -325,12 +451,25 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.59999389629810485"/>
+          <bgColor rgb="FFFFAFAF"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -347,12 +486,25 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.59999389629810485"/>
+          <bgColor theme="9" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -369,12 +521,25 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
+          <bgColor theme="8" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -391,12 +556,25 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor theme="3" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right style="thin">
@@ -409,14 +587,6 @@
           <color indexed="64"/>
         </bottom>
       </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="2" tint="-9.9978637043366805E-2"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -452,6 +622,72 @@
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
     <mruColors>
       <color rgb="FFAEFEFC"/>
       <color rgb="FFFFAFAF"/>
@@ -469,19 +705,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{ACB43508-5842-4AC2-BD97-169C49112CFD}" name="Table2" displayName="Table2" ref="A1:J194" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{ACB43508-5842-4AC2-BD97-169C49112CFD}" name="Table2" displayName="Table2" ref="A1:J194" totalsRowShown="0" headerRowDxfId="11" dataDxfId="0">
   <autoFilter ref="A1:J194" xr:uid="{604975D1-C3EC-46A6-858F-FDF4BF9CABB6}"/>
   <tableColumns count="10">
-    <tableColumn id="9" xr3:uid="{93A51A10-3E81-4CC9-A5BC-4EF29A6D94BA}" name="Livreur" dataDxfId="9"/>
-    <tableColumn id="1" xr3:uid="{303CFF24-5274-452D-983A-ADF8EC9130D4}" name="T.Colis" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{C2534D2C-BBEA-4061-B7A9-0124A7FE1B0B}" name="Livrés" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{3465882C-5C7B-4155-8240-51B30AEEF67B}" name="Non Livrés" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{A09613C1-1CBF-4D43-8F09-8759CA0C49DD}" name="Injoignable" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{DDC9BD68-77A4-4FAD-B53F-F0205BDAB779}" name="Réfuses" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{03C81CE8-C4D3-495B-B100-6FFB8BB8A84C}" name="Ajournée" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{57C72095-BA51-4590-9BEC-754B8C9591B3}" name="R.Récupéré" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{AC72D499-172D-419F-A115-0643F6084C79}" name="R.Livré" dataDxfId="0"/>
-    <tableColumn id="18" xr3:uid="{6504245F-2685-482D-81CA-4671AE4FAC90}" name="SR% (F)" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{93A51A10-3E81-4CC9-A5BC-4EF29A6D94BA}" name="Livreur" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{303CFF24-5274-452D-983A-ADF8EC9130D4}" name="T.Colis" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{C2534D2C-BBEA-4061-B7A9-0124A7FE1B0B}" name="Livrés" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{3465882C-5C7B-4155-8240-51B30AEEF67B}" name="Non Livrés" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{A09613C1-1CBF-4D43-8F09-8759CA0C49DD}" name="Injoignable" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{DDC9BD68-77A4-4FAD-B53F-F0205BDAB779}" name="Réfuses" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{03C81CE8-C4D3-495B-B100-6FFB8BB8A84C}" name="Ajournée" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{57C72095-BA51-4590-9BEC-754B8C9591B3}" name="R.Récupéré" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{AC72D499-172D-419F-A115-0643F6084C79}" name="R.Ajourné" dataDxfId="2"/>
+    <tableColumn id="18" xr3:uid="{6504245F-2685-482D-81CA-4671AE4FAC90}" name="SR% (F)" dataDxfId="1">
+      <calculatedColumnFormula>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -492,10 +730,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr val="windowText" lastClr="D8DEE9"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="2E3440"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -751,19 +989,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J194"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.109375" style="1" customWidth="1"/>
-    <col min="2" max="10" width="18.88671875" style="1" customWidth="1"/>
-    <col min="11" max="25" width="18.88671875" customWidth="1"/>
+    <col min="1" max="1" width="40.140625" style="1" customWidth="1"/>
+    <col min="2" max="10" width="18.85546875" style="1" customWidth="1"/>
+    <col min="11" max="25" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -781,2330 +1019,2909 @@
         <v>4</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="9"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="5"/>
       <c r="D2" s="6"/>
       <c r="E2" s="7"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="4"/>
-    </row>
-    <row r="3" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H2" s="5"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="9"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="5"/>
       <c r="D3" s="6"/>
       <c r="E3" s="7"/>
       <c r="F3" s="8"/>
       <c r="G3" s="8"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="4"/>
-    </row>
-    <row r="4" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H3" s="5"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="9"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="7"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="4"/>
-    </row>
-    <row r="5" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H4" s="5"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="9"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="5"/>
       <c r="D5" s="6"/>
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="4"/>
-    </row>
-    <row r="6" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H5" s="5"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="9"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="5"/>
       <c r="D6" s="6"/>
       <c r="E6" s="7"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="4"/>
-    </row>
-    <row r="7" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H6" s="5"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="9"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="5"/>
       <c r="D7" s="6"/>
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="4"/>
-    </row>
-    <row r="8" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H7" s="5"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="9"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="5"/>
       <c r="D8" s="6"/>
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="4"/>
-    </row>
-    <row r="9" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H8" s="5"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="9"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="5"/>
       <c r="D9" s="6"/>
       <c r="E9" s="7"/>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="4"/>
-    </row>
-    <row r="10" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H9" s="5"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="9"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="5"/>
       <c r="D10" s="6"/>
       <c r="E10" s="7"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="4"/>
-    </row>
-    <row r="11" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H10" s="5"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="9"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="5"/>
       <c r="D11" s="6"/>
       <c r="E11" s="7"/>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="4"/>
-    </row>
-    <row r="12" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H11" s="5"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="9"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="5"/>
       <c r="D12" s="6"/>
       <c r="E12" s="7"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="4"/>
-    </row>
-    <row r="13" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H12" s="5"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="9"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="5"/>
       <c r="D13" s="6"/>
       <c r="E13" s="7"/>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="4"/>
-    </row>
-    <row r="14" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H13" s="5"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="9"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="5"/>
       <c r="D14" s="6"/>
       <c r="E14" s="7"/>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="4"/>
-    </row>
-    <row r="15" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H14" s="5"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="9"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="5"/>
       <c r="D15" s="6"/>
       <c r="E15" s="7"/>
       <c r="F15" s="8"/>
       <c r="G15" s="8"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="4"/>
-    </row>
-    <row r="16" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H15" s="5"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="9"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="5"/>
       <c r="D16" s="6"/>
       <c r="E16" s="7"/>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="4"/>
-    </row>
-    <row r="17" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H16" s="5"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="9"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="5"/>
       <c r="D17" s="6"/>
       <c r="E17" s="7"/>
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="4"/>
-    </row>
-    <row r="18" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H17" s="5"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="9"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="5"/>
       <c r="D18" s="6"/>
       <c r="E18" s="7"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="4"/>
-    </row>
-    <row r="19" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H18" s="5"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="9"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="5"/>
       <c r="D19" s="6"/>
       <c r="E19" s="7"/>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="4"/>
-    </row>
-    <row r="20" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H19" s="5"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="9"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="5"/>
       <c r="D20" s="6"/>
       <c r="E20" s="7"/>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="4"/>
-    </row>
-    <row r="21" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H20" s="5"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="9"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="5"/>
       <c r="D21" s="6"/>
       <c r="E21" s="7"/>
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="4"/>
-    </row>
-    <row r="22" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H21" s="5"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="9"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="5"/>
       <c r="D22" s="6"/>
       <c r="E22" s="7"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="4"/>
-    </row>
-    <row r="23" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H22" s="5"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="9"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="5"/>
       <c r="D23" s="6"/>
       <c r="E23" s="7"/>
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="4"/>
-    </row>
-    <row r="24" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H23" s="5"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="9"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="5"/>
       <c r="D24" s="6"/>
       <c r="E24" s="7"/>
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="4"/>
-    </row>
-    <row r="25" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H24" s="5"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="9"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="5"/>
       <c r="D25" s="6"/>
       <c r="E25" s="7"/>
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="4"/>
-    </row>
-    <row r="26" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H25" s="5"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="9"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="5"/>
       <c r="D26" s="6"/>
       <c r="E26" s="7"/>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="4"/>
-    </row>
-    <row r="27" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H26" s="5"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="9"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="5"/>
       <c r="D27" s="6"/>
       <c r="E27" s="7"/>
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="4"/>
-    </row>
-    <row r="28" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H27" s="5"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="9"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="5"/>
       <c r="D28" s="6"/>
       <c r="E28" s="7"/>
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="4"/>
-    </row>
-    <row r="29" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H28" s="5"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="9"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="5"/>
       <c r="D29" s="6"/>
       <c r="E29" s="7"/>
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="4"/>
-    </row>
-    <row r="30" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H29" s="5"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="9"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="5"/>
       <c r="D30" s="6"/>
       <c r="E30" s="7"/>
       <c r="F30" s="8"/>
       <c r="G30" s="8"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="4"/>
-    </row>
-    <row r="31" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H30" s="5"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="9"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="5"/>
       <c r="D31" s="6"/>
       <c r="E31" s="7"/>
       <c r="F31" s="8"/>
       <c r="G31" s="8"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="4"/>
-    </row>
-    <row r="32" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H31" s="5"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="9"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="5"/>
       <c r="D32" s="6"/>
       <c r="E32" s="7"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="4"/>
-    </row>
-    <row r="33" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H32" s="5"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="9"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="5"/>
       <c r="D33" s="6"/>
       <c r="E33" s="7"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="4"/>
-    </row>
-    <row r="34" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H33" s="5"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="9"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="5"/>
       <c r="D34" s="6"/>
       <c r="E34" s="7"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="4"/>
-    </row>
-    <row r="35" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H34" s="5"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="9"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="5"/>
       <c r="D35" s="6"/>
       <c r="E35" s="7"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="4"/>
-    </row>
-    <row r="36" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H35" s="5"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="9"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="5"/>
       <c r="D36" s="6"/>
       <c r="E36" s="7"/>
       <c r="F36" s="8"/>
       <c r="G36" s="8"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="4"/>
-    </row>
-    <row r="37" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H36" s="5"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="9"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="5"/>
       <c r="D37" s="6"/>
       <c r="E37" s="7"/>
       <c r="F37" s="8"/>
       <c r="G37" s="8"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="4"/>
-    </row>
-    <row r="38" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H37" s="5"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
-      <c r="B38" s="5"/>
-      <c r="C38" s="9"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="5"/>
       <c r="D38" s="6"/>
       <c r="E38" s="7"/>
       <c r="F38" s="8"/>
       <c r="G38" s="8"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="4"/>
-    </row>
-    <row r="39" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H38" s="5"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="9"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="5"/>
       <c r="D39" s="6"/>
       <c r="E39" s="7"/>
       <c r="F39" s="8"/>
       <c r="G39" s="8"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="4"/>
-    </row>
-    <row r="40" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H39" s="5"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="9"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="5"/>
       <c r="D40" s="6"/>
       <c r="E40" s="7"/>
       <c r="F40" s="8"/>
       <c r="G40" s="8"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="4"/>
-    </row>
-    <row r="41" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H40" s="5"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="9"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="5"/>
       <c r="D41" s="6"/>
       <c r="E41" s="7"/>
       <c r="F41" s="8"/>
       <c r="G41" s="8"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="4"/>
-    </row>
-    <row r="42" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H41" s="5"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
-      <c r="B42" s="5"/>
-      <c r="C42" s="9"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="5"/>
       <c r="D42" s="6"/>
       <c r="E42" s="7"/>
       <c r="F42" s="8"/>
       <c r="G42" s="8"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="10"/>
-      <c r="J42" s="4"/>
-    </row>
-    <row r="43" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H42" s="5"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="9"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="5"/>
       <c r="D43" s="6"/>
       <c r="E43" s="7"/>
       <c r="F43" s="8"/>
       <c r="G43" s="8"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="4"/>
-    </row>
-    <row r="44" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H43" s="5"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
-      <c r="B44" s="5"/>
-      <c r="C44" s="9"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="5"/>
       <c r="D44" s="6"/>
       <c r="E44" s="7"/>
       <c r="F44" s="8"/>
       <c r="G44" s="8"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="4"/>
-    </row>
-    <row r="45" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H44" s="5"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="9"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="5"/>
       <c r="D45" s="6"/>
       <c r="E45" s="7"/>
       <c r="F45" s="8"/>
       <c r="G45" s="8"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="4"/>
-    </row>
-    <row r="46" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H45" s="5"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
-      <c r="B46" s="5"/>
-      <c r="C46" s="9"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="5"/>
       <c r="D46" s="6"/>
       <c r="E46" s="7"/>
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="4"/>
-    </row>
-    <row r="47" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H46" s="5"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
-      <c r="B47" s="5"/>
-      <c r="C47" s="9"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="5"/>
       <c r="D47" s="6"/>
       <c r="E47" s="7"/>
       <c r="F47" s="8"/>
       <c r="G47" s="8"/>
-      <c r="H47" s="9"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="4"/>
-    </row>
-    <row r="48" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H47" s="5"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
-      <c r="B48" s="5"/>
-      <c r="C48" s="9"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="5"/>
       <c r="D48" s="6"/>
       <c r="E48" s="7"/>
       <c r="F48" s="8"/>
       <c r="G48" s="8"/>
-      <c r="H48" s="9"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="4"/>
-    </row>
-    <row r="49" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H48" s="5"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
-      <c r="B49" s="5"/>
-      <c r="C49" s="9"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="5"/>
       <c r="D49" s="6"/>
       <c r="E49" s="7"/>
       <c r="F49" s="8"/>
       <c r="G49" s="8"/>
-      <c r="H49" s="9"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="4"/>
-    </row>
-    <row r="50" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H49" s="5"/>
+      <c r="I49" s="9"/>
+      <c r="J49" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
-      <c r="B50" s="5"/>
-      <c r="C50" s="9"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="5"/>
       <c r="D50" s="6"/>
       <c r="E50" s="7"/>
       <c r="F50" s="8"/>
       <c r="G50" s="8"/>
-      <c r="H50" s="9"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="4"/>
-    </row>
-    <row r="51" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H50" s="5"/>
+      <c r="I50" s="9"/>
+      <c r="J50" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="9"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="5"/>
       <c r="D51" s="6"/>
       <c r="E51" s="7"/>
       <c r="F51" s="8"/>
       <c r="G51" s="8"/>
-      <c r="H51" s="9"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="4"/>
-    </row>
-    <row r="52" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H51" s="5"/>
+      <c r="I51" s="9"/>
+      <c r="J51" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3"/>
-      <c r="B52" s="5"/>
-      <c r="C52" s="9"/>
+      <c r="B52" s="4"/>
+      <c r="C52" s="5"/>
       <c r="D52" s="6"/>
       <c r="E52" s="7"/>
       <c r="F52" s="8"/>
       <c r="G52" s="8"/>
-      <c r="H52" s="9"/>
-      <c r="I52" s="10"/>
-      <c r="J52" s="4"/>
-    </row>
-    <row r="53" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H52" s="5"/>
+      <c r="I52" s="9"/>
+      <c r="J52" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
-      <c r="B53" s="5"/>
-      <c r="C53" s="9"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="5"/>
       <c r="D53" s="6"/>
       <c r="E53" s="7"/>
       <c r="F53" s="8"/>
       <c r="G53" s="8"/>
-      <c r="H53" s="9"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="4"/>
-    </row>
-    <row r="54" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H53" s="5"/>
+      <c r="I53" s="9"/>
+      <c r="J53" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3"/>
-      <c r="B54" s="5"/>
-      <c r="C54" s="9"/>
+      <c r="B54" s="4"/>
+      <c r="C54" s="5"/>
       <c r="D54" s="6"/>
       <c r="E54" s="7"/>
       <c r="F54" s="8"/>
       <c r="G54" s="8"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="4"/>
-    </row>
-    <row r="55" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H54" s="5"/>
+      <c r="I54" s="9"/>
+      <c r="J54" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
-      <c r="B55" s="5"/>
-      <c r="C55" s="9"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="5"/>
       <c r="D55" s="6"/>
       <c r="E55" s="7"/>
       <c r="F55" s="8"/>
       <c r="G55" s="8"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="10"/>
-      <c r="J55" s="4"/>
-    </row>
-    <row r="56" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H55" s="5"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3"/>
-      <c r="B56" s="5"/>
-      <c r="C56" s="9"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="5"/>
       <c r="D56" s="6"/>
       <c r="E56" s="7"/>
       <c r="F56" s="8"/>
       <c r="G56" s="8"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="10"/>
-      <c r="J56" s="4"/>
-    </row>
-    <row r="57" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H56" s="5"/>
+      <c r="I56" s="9"/>
+      <c r="J56" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3"/>
-      <c r="B57" s="5"/>
-      <c r="C57" s="9"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="5"/>
       <c r="D57" s="6"/>
       <c r="E57" s="7"/>
       <c r="F57" s="8"/>
       <c r="G57" s="8"/>
-      <c r="H57" s="9"/>
-      <c r="I57" s="10"/>
-      <c r="J57" s="4"/>
-    </row>
-    <row r="58" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H57" s="5"/>
+      <c r="I57" s="9"/>
+      <c r="J57" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3"/>
-      <c r="B58" s="5"/>
-      <c r="C58" s="9"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="5"/>
       <c r="D58" s="6"/>
       <c r="E58" s="7"/>
       <c r="F58" s="8"/>
       <c r="G58" s="8"/>
-      <c r="H58" s="9"/>
-      <c r="I58" s="10"/>
-      <c r="J58" s="4"/>
-    </row>
-    <row r="59" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H58" s="5"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3"/>
-      <c r="B59" s="5"/>
-      <c r="C59" s="9"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="5"/>
       <c r="D59" s="6"/>
       <c r="E59" s="7"/>
       <c r="F59" s="8"/>
       <c r="G59" s="8"/>
-      <c r="H59" s="9"/>
-      <c r="I59" s="10"/>
-      <c r="J59" s="4"/>
-    </row>
-    <row r="60" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H59" s="5"/>
+      <c r="I59" s="9"/>
+      <c r="J59" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3"/>
-      <c r="B60" s="5"/>
-      <c r="C60" s="9"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="5"/>
       <c r="D60" s="6"/>
       <c r="E60" s="7"/>
       <c r="F60" s="8"/>
       <c r="G60" s="8"/>
-      <c r="H60" s="9"/>
-      <c r="I60" s="10"/>
-      <c r="J60" s="4"/>
-    </row>
-    <row r="61" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H60" s="5"/>
+      <c r="I60" s="9"/>
+      <c r="J60" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
-      <c r="B61" s="5"/>
-      <c r="C61" s="9"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="5"/>
       <c r="D61" s="6"/>
       <c r="E61" s="7"/>
       <c r="F61" s="8"/>
       <c r="G61" s="8"/>
-      <c r="H61" s="9"/>
-      <c r="I61" s="10"/>
-      <c r="J61" s="4"/>
-    </row>
-    <row r="62" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H61" s="5"/>
+      <c r="I61" s="9"/>
+      <c r="J61" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3"/>
-      <c r="B62" s="5"/>
-      <c r="C62" s="9"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="5"/>
       <c r="D62" s="6"/>
       <c r="E62" s="7"/>
       <c r="F62" s="8"/>
       <c r="G62" s="8"/>
-      <c r="H62" s="9"/>
-      <c r="I62" s="10"/>
-      <c r="J62" s="4"/>
-    </row>
-    <row r="63" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H62" s="5"/>
+      <c r="I62" s="9"/>
+      <c r="J62" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="9"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="5"/>
       <c r="D63" s="6"/>
       <c r="E63" s="7"/>
       <c r="F63" s="8"/>
       <c r="G63" s="8"/>
-      <c r="H63" s="9"/>
-      <c r="I63" s="10"/>
-      <c r="J63" s="4"/>
-    </row>
-    <row r="64" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H63" s="5"/>
+      <c r="I63" s="9"/>
+      <c r="J63" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3"/>
-      <c r="B64" s="5"/>
-      <c r="C64" s="9"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="5"/>
       <c r="D64" s="6"/>
       <c r="E64" s="7"/>
       <c r="F64" s="8"/>
       <c r="G64" s="8"/>
-      <c r="H64" s="9"/>
-      <c r="I64" s="10"/>
-      <c r="J64" s="4"/>
-    </row>
-    <row r="65" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H64" s="5"/>
+      <c r="I64" s="9"/>
+      <c r="J64" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3"/>
-      <c r="B65" s="5"/>
-      <c r="C65" s="9"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="5"/>
       <c r="D65" s="6"/>
       <c r="E65" s="7"/>
       <c r="F65" s="8"/>
       <c r="G65" s="8"/>
-      <c r="H65" s="9"/>
-      <c r="I65" s="10"/>
-      <c r="J65" s="4"/>
-    </row>
-    <row r="66" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H65" s="5"/>
+      <c r="I65" s="9"/>
+      <c r="J65" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3"/>
-      <c r="B66" s="5"/>
-      <c r="C66" s="9"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="5"/>
       <c r="D66" s="6"/>
       <c r="E66" s="7"/>
       <c r="F66" s="8"/>
       <c r="G66" s="8"/>
-      <c r="H66" s="9"/>
-      <c r="I66" s="10"/>
-      <c r="J66" s="4"/>
-    </row>
-    <row r="67" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H66" s="5"/>
+      <c r="I66" s="9"/>
+      <c r="J66" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="9"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="5"/>
       <c r="D67" s="6"/>
       <c r="E67" s="7"/>
       <c r="F67" s="8"/>
       <c r="G67" s="8"/>
-      <c r="H67" s="9"/>
-      <c r="I67" s="10"/>
-      <c r="J67" s="4"/>
-    </row>
-    <row r="68" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H67" s="5"/>
+      <c r="I67" s="9"/>
+      <c r="J67" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="9"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="5"/>
       <c r="D68" s="6"/>
       <c r="E68" s="7"/>
       <c r="F68" s="8"/>
       <c r="G68" s="8"/>
-      <c r="H68" s="9"/>
-      <c r="I68" s="10"/>
-      <c r="J68" s="4"/>
-    </row>
-    <row r="69" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H68" s="5"/>
+      <c r="I68" s="9"/>
+      <c r="J68" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3"/>
-      <c r="B69" s="5"/>
-      <c r="C69" s="9"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="5"/>
       <c r="D69" s="6"/>
       <c r="E69" s="7"/>
       <c r="F69" s="8"/>
       <c r="G69" s="8"/>
-      <c r="H69" s="9"/>
-      <c r="I69" s="10"/>
-      <c r="J69" s="4"/>
-    </row>
-    <row r="70" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H69" s="5"/>
+      <c r="I69" s="9"/>
+      <c r="J69" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="9"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="5"/>
       <c r="D70" s="6"/>
       <c r="E70" s="7"/>
       <c r="F70" s="8"/>
       <c r="G70" s="8"/>
-      <c r="H70" s="9"/>
-      <c r="I70" s="10"/>
-      <c r="J70" s="4"/>
-    </row>
-    <row r="71" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H70" s="5"/>
+      <c r="I70" s="9"/>
+      <c r="J70" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="9"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="5"/>
       <c r="D71" s="6"/>
       <c r="E71" s="7"/>
       <c r="F71" s="8"/>
       <c r="G71" s="8"/>
-      <c r="H71" s="9"/>
-      <c r="I71" s="10"/>
-      <c r="J71" s="4"/>
-    </row>
-    <row r="72" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H71" s="5"/>
+      <c r="I71" s="9"/>
+      <c r="J71" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="9"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="5"/>
       <c r="D72" s="6"/>
       <c r="E72" s="7"/>
       <c r="F72" s="8"/>
       <c r="G72" s="8"/>
-      <c r="H72" s="9"/>
-      <c r="I72" s="10"/>
-      <c r="J72" s="4"/>
-    </row>
-    <row r="73" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H72" s="5"/>
+      <c r="I72" s="9"/>
+      <c r="J72" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
-      <c r="B73" s="5"/>
-      <c r="C73" s="9"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="5"/>
       <c r="D73" s="6"/>
       <c r="E73" s="7"/>
       <c r="F73" s="8"/>
       <c r="G73" s="8"/>
-      <c r="H73" s="9"/>
-      <c r="I73" s="10"/>
-      <c r="J73" s="4"/>
-    </row>
-    <row r="74" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H73" s="5"/>
+      <c r="I73" s="9"/>
+      <c r="J73" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3"/>
-      <c r="B74" s="5"/>
-      <c r="C74" s="9"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="5"/>
       <c r="D74" s="6"/>
       <c r="E74" s="7"/>
       <c r="F74" s="8"/>
       <c r="G74" s="8"/>
-      <c r="H74" s="9"/>
-      <c r="I74" s="10"/>
-      <c r="J74" s="4"/>
-    </row>
-    <row r="75" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H74" s="5"/>
+      <c r="I74" s="9"/>
+      <c r="J74" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="9"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="5"/>
       <c r="D75" s="6"/>
       <c r="E75" s="7"/>
       <c r="F75" s="8"/>
       <c r="G75" s="8"/>
-      <c r="H75" s="9"/>
-      <c r="I75" s="10"/>
-      <c r="J75" s="4"/>
-    </row>
-    <row r="76" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H75" s="5"/>
+      <c r="I75" s="9"/>
+      <c r="J75" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3"/>
-      <c r="B76" s="5"/>
-      <c r="C76" s="9"/>
+      <c r="B76" s="4"/>
+      <c r="C76" s="5"/>
       <c r="D76" s="6"/>
       <c r="E76" s="7"/>
       <c r="F76" s="8"/>
       <c r="G76" s="8"/>
-      <c r="H76" s="9"/>
-      <c r="I76" s="10"/>
-      <c r="J76" s="4"/>
-    </row>
-    <row r="77" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H76" s="5"/>
+      <c r="I76" s="9"/>
+      <c r="J76" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="9"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="5"/>
       <c r="D77" s="6"/>
       <c r="E77" s="7"/>
       <c r="F77" s="8"/>
       <c r="G77" s="8"/>
-      <c r="H77" s="9"/>
-      <c r="I77" s="10"/>
-      <c r="J77" s="4"/>
-    </row>
-    <row r="78" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H77" s="5"/>
+      <c r="I77" s="9"/>
+      <c r="J77" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3"/>
-      <c r="B78" s="5"/>
-      <c r="C78" s="9"/>
+      <c r="B78" s="4"/>
+      <c r="C78" s="5"/>
       <c r="D78" s="6"/>
       <c r="E78" s="7"/>
       <c r="F78" s="8"/>
       <c r="G78" s="8"/>
-      <c r="H78" s="9"/>
-      <c r="I78" s="10"/>
-      <c r="J78" s="4"/>
-    </row>
-    <row r="79" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H78" s="5"/>
+      <c r="I78" s="9"/>
+      <c r="J78" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3"/>
-      <c r="B79" s="5"/>
-      <c r="C79" s="9"/>
+      <c r="B79" s="4"/>
+      <c r="C79" s="5"/>
       <c r="D79" s="6"/>
       <c r="E79" s="7"/>
       <c r="F79" s="8"/>
       <c r="G79" s="8"/>
-      <c r="H79" s="9"/>
-      <c r="I79" s="10"/>
-      <c r="J79" s="4"/>
-    </row>
-    <row r="80" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H79" s="5"/>
+      <c r="I79" s="9"/>
+      <c r="J79" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3"/>
-      <c r="B80" s="5"/>
-      <c r="C80" s="9"/>
+      <c r="B80" s="4"/>
+      <c r="C80" s="5"/>
       <c r="D80" s="6"/>
       <c r="E80" s="7"/>
       <c r="F80" s="8"/>
       <c r="G80" s="8"/>
-      <c r="H80" s="9"/>
-      <c r="I80" s="10"/>
-      <c r="J80" s="4"/>
-    </row>
-    <row r="81" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H80" s="5"/>
+      <c r="I80" s="9"/>
+      <c r="J80" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3"/>
-      <c r="B81" s="5"/>
-      <c r="C81" s="9"/>
+      <c r="B81" s="4"/>
+      <c r="C81" s="5"/>
       <c r="D81" s="6"/>
       <c r="E81" s="7"/>
       <c r="F81" s="8"/>
       <c r="G81" s="8"/>
-      <c r="H81" s="9"/>
-      <c r="I81" s="10"/>
-      <c r="J81" s="4"/>
-    </row>
-    <row r="82" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H81" s="5"/>
+      <c r="I81" s="9"/>
+      <c r="J81" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3"/>
-      <c r="B82" s="5"/>
-      <c r="C82" s="9"/>
+      <c r="B82" s="4"/>
+      <c r="C82" s="5"/>
       <c r="D82" s="6"/>
       <c r="E82" s="7"/>
       <c r="F82" s="8"/>
       <c r="G82" s="8"/>
-      <c r="H82" s="9"/>
-      <c r="I82" s="10"/>
-      <c r="J82" s="4"/>
-    </row>
-    <row r="83" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H82" s="5"/>
+      <c r="I82" s="9"/>
+      <c r="J82" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3"/>
-      <c r="B83" s="5"/>
-      <c r="C83" s="9"/>
+      <c r="B83" s="4"/>
+      <c r="C83" s="5"/>
       <c r="D83" s="6"/>
       <c r="E83" s="7"/>
       <c r="F83" s="8"/>
       <c r="G83" s="8"/>
-      <c r="H83" s="9"/>
-      <c r="I83" s="10"/>
-      <c r="J83" s="4"/>
-    </row>
-    <row r="84" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H83" s="5"/>
+      <c r="I83" s="9"/>
+      <c r="J83" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3"/>
-      <c r="B84" s="5"/>
-      <c r="C84" s="9"/>
+      <c r="B84" s="4"/>
+      <c r="C84" s="5"/>
       <c r="D84" s="6"/>
       <c r="E84" s="7"/>
       <c r="F84" s="8"/>
       <c r="G84" s="8"/>
-      <c r="H84" s="9"/>
-      <c r="I84" s="10"/>
-      <c r="J84" s="4"/>
-    </row>
-    <row r="85" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H84" s="5"/>
+      <c r="I84" s="9"/>
+      <c r="J84" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3"/>
-      <c r="B85" s="5"/>
-      <c r="C85" s="9"/>
+      <c r="B85" s="4"/>
+      <c r="C85" s="5"/>
       <c r="D85" s="6"/>
       <c r="E85" s="7"/>
       <c r="F85" s="8"/>
       <c r="G85" s="8"/>
-      <c r="H85" s="9"/>
-      <c r="I85" s="10"/>
-      <c r="J85" s="4"/>
-    </row>
-    <row r="86" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H85" s="5"/>
+      <c r="I85" s="9"/>
+      <c r="J85" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3"/>
-      <c r="B86" s="5"/>
-      <c r="C86" s="9"/>
+      <c r="B86" s="4"/>
+      <c r="C86" s="5"/>
       <c r="D86" s="6"/>
       <c r="E86" s="7"/>
       <c r="F86" s="8"/>
       <c r="G86" s="8"/>
-      <c r="H86" s="9"/>
-      <c r="I86" s="10"/>
-      <c r="J86" s="4"/>
-    </row>
-    <row r="87" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H86" s="5"/>
+      <c r="I86" s="9"/>
+      <c r="J86" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3"/>
-      <c r="B87" s="5"/>
-      <c r="C87" s="9"/>
+      <c r="B87" s="4"/>
+      <c r="C87" s="5"/>
       <c r="D87" s="6"/>
       <c r="E87" s="7"/>
       <c r="F87" s="8"/>
       <c r="G87" s="8"/>
-      <c r="H87" s="9"/>
-      <c r="I87" s="10"/>
-      <c r="J87" s="4"/>
-    </row>
-    <row r="88" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H87" s="5"/>
+      <c r="I87" s="9"/>
+      <c r="J87" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3"/>
-      <c r="B88" s="5"/>
-      <c r="C88" s="9"/>
+      <c r="B88" s="4"/>
+      <c r="C88" s="5"/>
       <c r="D88" s="6"/>
       <c r="E88" s="7"/>
       <c r="F88" s="8"/>
       <c r="G88" s="8"/>
-      <c r="H88" s="9"/>
-      <c r="I88" s="10"/>
-      <c r="J88" s="4"/>
-    </row>
-    <row r="89" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H88" s="5"/>
+      <c r="I88" s="9"/>
+      <c r="J88" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3"/>
-      <c r="B89" s="5"/>
-      <c r="C89" s="9"/>
+      <c r="B89" s="4"/>
+      <c r="C89" s="5"/>
       <c r="D89" s="6"/>
       <c r="E89" s="7"/>
       <c r="F89" s="8"/>
       <c r="G89" s="8"/>
-      <c r="H89" s="9"/>
-      <c r="I89" s="10"/>
-      <c r="J89" s="4"/>
-    </row>
-    <row r="90" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H89" s="5"/>
+      <c r="I89" s="9"/>
+      <c r="J89" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3"/>
-      <c r="B90" s="5"/>
-      <c r="C90" s="9"/>
+      <c r="B90" s="4"/>
+      <c r="C90" s="5"/>
       <c r="D90" s="6"/>
       <c r="E90" s="7"/>
       <c r="F90" s="8"/>
       <c r="G90" s="8"/>
-      <c r="H90" s="9"/>
-      <c r="I90" s="10"/>
-      <c r="J90" s="4"/>
-    </row>
-    <row r="91" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H90" s="5"/>
+      <c r="I90" s="9"/>
+      <c r="J90" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3"/>
-      <c r="B91" s="5"/>
-      <c r="C91" s="9"/>
+      <c r="B91" s="4"/>
+      <c r="C91" s="5"/>
       <c r="D91" s="6"/>
       <c r="E91" s="7"/>
       <c r="F91" s="8"/>
       <c r="G91" s="8"/>
-      <c r="H91" s="9"/>
-      <c r="I91" s="10"/>
-      <c r="J91" s="4"/>
-    </row>
-    <row r="92" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H91" s="5"/>
+      <c r="I91" s="9"/>
+      <c r="J91" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3"/>
-      <c r="B92" s="5"/>
-      <c r="C92" s="9"/>
+      <c r="B92" s="4"/>
+      <c r="C92" s="5"/>
       <c r="D92" s="6"/>
       <c r="E92" s="7"/>
       <c r="F92" s="8"/>
       <c r="G92" s="8"/>
-      <c r="H92" s="9"/>
-      <c r="I92" s="10"/>
-      <c r="J92" s="4"/>
-    </row>
-    <row r="93" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H92" s="5"/>
+      <c r="I92" s="9"/>
+      <c r="J92" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3"/>
-      <c r="B93" s="5"/>
-      <c r="C93" s="9"/>
+      <c r="B93" s="4"/>
+      <c r="C93" s="5"/>
       <c r="D93" s="6"/>
       <c r="E93" s="7"/>
       <c r="F93" s="8"/>
       <c r="G93" s="8"/>
-      <c r="H93" s="9"/>
-      <c r="I93" s="10"/>
-      <c r="J93" s="4"/>
-    </row>
-    <row r="94" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H93" s="5"/>
+      <c r="I93" s="9"/>
+      <c r="J93" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3"/>
-      <c r="B94" s="5"/>
-      <c r="C94" s="9"/>
+      <c r="B94" s="4"/>
+      <c r="C94" s="5"/>
       <c r="D94" s="6"/>
       <c r="E94" s="7"/>
       <c r="F94" s="8"/>
       <c r="G94" s="8"/>
-      <c r="H94" s="9"/>
-      <c r="I94" s="10"/>
-      <c r="J94" s="4"/>
-    </row>
-    <row r="95" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H94" s="5"/>
+      <c r="I94" s="9"/>
+      <c r="J94" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3"/>
-      <c r="B95" s="5"/>
-      <c r="C95" s="9"/>
+      <c r="B95" s="4"/>
+      <c r="C95" s="5"/>
       <c r="D95" s="6"/>
       <c r="E95" s="7"/>
       <c r="F95" s="8"/>
       <c r="G95" s="8"/>
-      <c r="H95" s="9"/>
-      <c r="I95" s="10"/>
-      <c r="J95" s="4"/>
-    </row>
-    <row r="96" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H95" s="5"/>
+      <c r="I95" s="9"/>
+      <c r="J95" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3"/>
-      <c r="B96" s="5"/>
-      <c r="C96" s="9"/>
+      <c r="B96" s="4"/>
+      <c r="C96" s="5"/>
       <c r="D96" s="6"/>
       <c r="E96" s="7"/>
       <c r="F96" s="8"/>
       <c r="G96" s="8"/>
-      <c r="H96" s="9"/>
-      <c r="I96" s="10"/>
-      <c r="J96" s="4"/>
-    </row>
-    <row r="97" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H96" s="5"/>
+      <c r="I96" s="9"/>
+      <c r="J96" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3"/>
-      <c r="B97" s="5"/>
-      <c r="C97" s="9"/>
+      <c r="B97" s="4"/>
+      <c r="C97" s="5"/>
       <c r="D97" s="6"/>
       <c r="E97" s="7"/>
       <c r="F97" s="8"/>
       <c r="G97" s="8"/>
-      <c r="H97" s="9"/>
-      <c r="I97" s="10"/>
-      <c r="J97" s="4"/>
-    </row>
-    <row r="98" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H97" s="5"/>
+      <c r="I97" s="9"/>
+      <c r="J97" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3"/>
-      <c r="B98" s="5"/>
-      <c r="C98" s="9"/>
+      <c r="B98" s="4"/>
+      <c r="C98" s="5"/>
       <c r="D98" s="6"/>
       <c r="E98" s="7"/>
       <c r="F98" s="8"/>
       <c r="G98" s="8"/>
-      <c r="H98" s="9"/>
-      <c r="I98" s="10"/>
-      <c r="J98" s="4"/>
-    </row>
-    <row r="99" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H98" s="5"/>
+      <c r="I98" s="9"/>
+      <c r="J98" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
-      <c r="B99" s="5"/>
-      <c r="C99" s="9"/>
+      <c r="B99" s="4"/>
+      <c r="C99" s="5"/>
       <c r="D99" s="6"/>
       <c r="E99" s="7"/>
       <c r="F99" s="8"/>
       <c r="G99" s="8"/>
-      <c r="H99" s="9"/>
-      <c r="I99" s="10"/>
-      <c r="J99" s="4"/>
-    </row>
-    <row r="100" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H99" s="5"/>
+      <c r="I99" s="9"/>
+      <c r="J99" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3"/>
-      <c r="B100" s="5"/>
-      <c r="C100" s="9"/>
+      <c r="B100" s="4"/>
+      <c r="C100" s="5"/>
       <c r="D100" s="6"/>
       <c r="E100" s="7"/>
       <c r="F100" s="8"/>
       <c r="G100" s="8"/>
-      <c r="H100" s="9"/>
-      <c r="I100" s="10"/>
-      <c r="J100" s="4"/>
-    </row>
-    <row r="101" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H100" s="5"/>
+      <c r="I100" s="9"/>
+      <c r="J100" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3"/>
-      <c r="B101" s="5"/>
-      <c r="C101" s="9"/>
+      <c r="B101" s="4"/>
+      <c r="C101" s="5"/>
       <c r="D101" s="6"/>
       <c r="E101" s="7"/>
       <c r="F101" s="8"/>
       <c r="G101" s="8"/>
-      <c r="H101" s="9"/>
-      <c r="I101" s="10"/>
-      <c r="J101" s="4"/>
-    </row>
-    <row r="102" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H101" s="5"/>
+      <c r="I101" s="9"/>
+      <c r="J101" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3"/>
-      <c r="B102" s="5"/>
-      <c r="C102" s="9"/>
+      <c r="B102" s="4"/>
+      <c r="C102" s="5"/>
       <c r="D102" s="6"/>
       <c r="E102" s="7"/>
       <c r="F102" s="8"/>
       <c r="G102" s="8"/>
-      <c r="H102" s="9"/>
-      <c r="I102" s="10"/>
-      <c r="J102" s="4"/>
-    </row>
-    <row r="103" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H102" s="5"/>
+      <c r="I102" s="9"/>
+      <c r="J102" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3"/>
-      <c r="B103" s="5"/>
-      <c r="C103" s="9"/>
+      <c r="B103" s="4"/>
+      <c r="C103" s="5"/>
       <c r="D103" s="6"/>
       <c r="E103" s="7"/>
       <c r="F103" s="8"/>
       <c r="G103" s="8"/>
-      <c r="H103" s="9"/>
-      <c r="I103" s="10"/>
-      <c r="J103" s="4"/>
-    </row>
-    <row r="104" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H103" s="5"/>
+      <c r="I103" s="9"/>
+      <c r="J103" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3"/>
-      <c r="B104" s="5"/>
-      <c r="C104" s="9"/>
+      <c r="B104" s="4"/>
+      <c r="C104" s="5"/>
       <c r="D104" s="6"/>
       <c r="E104" s="7"/>
       <c r="F104" s="8"/>
       <c r="G104" s="8"/>
-      <c r="H104" s="9"/>
-      <c r="I104" s="10"/>
-      <c r="J104" s="4"/>
-    </row>
-    <row r="105" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H104" s="5"/>
+      <c r="I104" s="9"/>
+      <c r="J104" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3"/>
-      <c r="B105" s="5"/>
-      <c r="C105" s="9"/>
+      <c r="B105" s="4"/>
+      <c r="C105" s="5"/>
       <c r="D105" s="6"/>
       <c r="E105" s="7"/>
       <c r="F105" s="8"/>
       <c r="G105" s="8"/>
-      <c r="H105" s="9"/>
-      <c r="I105" s="10"/>
-      <c r="J105" s="4"/>
-    </row>
-    <row r="106" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H105" s="5"/>
+      <c r="I105" s="9"/>
+      <c r="J105" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3"/>
-      <c r="B106" s="5"/>
-      <c r="C106" s="9"/>
+      <c r="B106" s="4"/>
+      <c r="C106" s="5"/>
       <c r="D106" s="6"/>
       <c r="E106" s="7"/>
       <c r="F106" s="8"/>
       <c r="G106" s="8"/>
-      <c r="H106" s="9"/>
-      <c r="I106" s="10"/>
-      <c r="J106" s="4"/>
-    </row>
-    <row r="107" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H106" s="5"/>
+      <c r="I106" s="9"/>
+      <c r="J106" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3"/>
-      <c r="B107" s="5"/>
-      <c r="C107" s="9"/>
+      <c r="B107" s="4"/>
+      <c r="C107" s="5"/>
       <c r="D107" s="6"/>
       <c r="E107" s="7"/>
       <c r="F107" s="8"/>
       <c r="G107" s="8"/>
-      <c r="H107" s="9"/>
-      <c r="I107" s="10"/>
-      <c r="J107" s="4"/>
-    </row>
-    <row r="108" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H107" s="5"/>
+      <c r="I107" s="9"/>
+      <c r="J107" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3"/>
-      <c r="B108" s="5"/>
-      <c r="C108" s="9"/>
+      <c r="B108" s="4"/>
+      <c r="C108" s="5"/>
       <c r="D108" s="6"/>
       <c r="E108" s="7"/>
       <c r="F108" s="8"/>
       <c r="G108" s="8"/>
-      <c r="H108" s="9"/>
-      <c r="I108" s="10"/>
-      <c r="J108" s="4"/>
-    </row>
-    <row r="109" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H108" s="5"/>
+      <c r="I108" s="9"/>
+      <c r="J108" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3"/>
-      <c r="B109" s="5"/>
-      <c r="C109" s="9"/>
+      <c r="B109" s="4"/>
+      <c r="C109" s="5"/>
       <c r="D109" s="6"/>
       <c r="E109" s="7"/>
       <c r="F109" s="8"/>
       <c r="G109" s="8"/>
-      <c r="H109" s="9"/>
-      <c r="I109" s="10"/>
-      <c r="J109" s="4"/>
-    </row>
-    <row r="110" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H109" s="5"/>
+      <c r="I109" s="9"/>
+      <c r="J109" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3"/>
-      <c r="B110" s="5"/>
-      <c r="C110" s="9"/>
+      <c r="B110" s="4"/>
+      <c r="C110" s="5"/>
       <c r="D110" s="6"/>
       <c r="E110" s="7"/>
       <c r="F110" s="8"/>
       <c r="G110" s="8"/>
-      <c r="H110" s="9"/>
-      <c r="I110" s="10"/>
-      <c r="J110" s="4"/>
-    </row>
-    <row r="111" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H110" s="5"/>
+      <c r="I110" s="9"/>
+      <c r="J110" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3"/>
-      <c r="B111" s="5"/>
-      <c r="C111" s="9"/>
+      <c r="B111" s="4"/>
+      <c r="C111" s="5"/>
       <c r="D111" s="6"/>
       <c r="E111" s="7"/>
       <c r="F111" s="8"/>
       <c r="G111" s="8"/>
-      <c r="H111" s="9"/>
-      <c r="I111" s="10"/>
-      <c r="J111" s="4"/>
-    </row>
-    <row r="112" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H111" s="5"/>
+      <c r="I111" s="9"/>
+      <c r="J111" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3"/>
-      <c r="B112" s="5"/>
-      <c r="C112" s="9"/>
+      <c r="B112" s="4"/>
+      <c r="C112" s="5"/>
       <c r="D112" s="6"/>
       <c r="E112" s="7"/>
       <c r="F112" s="8"/>
       <c r="G112" s="8"/>
-      <c r="H112" s="9"/>
-      <c r="I112" s="10"/>
-      <c r="J112" s="4"/>
-    </row>
-    <row r="113" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H112" s="5"/>
+      <c r="I112" s="9"/>
+      <c r="J112" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3"/>
-      <c r="B113" s="5"/>
-      <c r="C113" s="9"/>
+      <c r="B113" s="4"/>
+      <c r="C113" s="5"/>
       <c r="D113" s="6"/>
       <c r="E113" s="7"/>
       <c r="F113" s="8"/>
       <c r="G113" s="8"/>
-      <c r="H113" s="9"/>
-      <c r="I113" s="10"/>
-      <c r="J113" s="4"/>
-    </row>
-    <row r="114" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H113" s="5"/>
+      <c r="I113" s="9"/>
+      <c r="J113" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3"/>
-      <c r="B114" s="5"/>
-      <c r="C114" s="9"/>
+      <c r="B114" s="4"/>
+      <c r="C114" s="5"/>
       <c r="D114" s="6"/>
       <c r="E114" s="7"/>
       <c r="F114" s="8"/>
       <c r="G114" s="8"/>
-      <c r="H114" s="9"/>
-      <c r="I114" s="10"/>
-      <c r="J114" s="4"/>
-    </row>
-    <row r="115" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H114" s="5"/>
+      <c r="I114" s="9"/>
+      <c r="J114" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3"/>
-      <c r="B115" s="5"/>
-      <c r="C115" s="9"/>
+      <c r="B115" s="4"/>
+      <c r="C115" s="5"/>
       <c r="D115" s="6"/>
       <c r="E115" s="7"/>
       <c r="F115" s="8"/>
       <c r="G115" s="8"/>
-      <c r="H115" s="9"/>
-      <c r="I115" s="10"/>
-      <c r="J115" s="4"/>
-    </row>
-    <row r="116" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H115" s="5"/>
+      <c r="I115" s="9"/>
+      <c r="J115" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3"/>
-      <c r="B116" s="5"/>
-      <c r="C116" s="9"/>
+      <c r="B116" s="4"/>
+      <c r="C116" s="5"/>
       <c r="D116" s="6"/>
       <c r="E116" s="7"/>
       <c r="F116" s="8"/>
       <c r="G116" s="8"/>
-      <c r="H116" s="9"/>
-      <c r="I116" s="10"/>
-      <c r="J116" s="4"/>
-    </row>
-    <row r="117" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H116" s="5"/>
+      <c r="I116" s="9"/>
+      <c r="J116" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="3"/>
-      <c r="B117" s="5"/>
-      <c r="C117" s="9"/>
+      <c r="B117" s="4"/>
+      <c r="C117" s="5"/>
       <c r="D117" s="6"/>
       <c r="E117" s="7"/>
       <c r="F117" s="8"/>
       <c r="G117" s="8"/>
-      <c r="H117" s="9"/>
-      <c r="I117" s="10"/>
-      <c r="J117" s="4"/>
-    </row>
-    <row r="118" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H117" s="5"/>
+      <c r="I117" s="9"/>
+      <c r="J117" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="3"/>
-      <c r="B118" s="5"/>
-      <c r="C118" s="9"/>
+      <c r="B118" s="4"/>
+      <c r="C118" s="5"/>
       <c r="D118" s="6"/>
       <c r="E118" s="7"/>
       <c r="F118" s="8"/>
       <c r="G118" s="8"/>
-      <c r="H118" s="9"/>
-      <c r="I118" s="10"/>
-      <c r="J118" s="4"/>
-    </row>
-    <row r="119" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H118" s="5"/>
+      <c r="I118" s="9"/>
+      <c r="J118" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="3"/>
-      <c r="B119" s="5"/>
-      <c r="C119" s="9"/>
+      <c r="B119" s="4"/>
+      <c r="C119" s="5"/>
       <c r="D119" s="6"/>
       <c r="E119" s="7"/>
       <c r="F119" s="8"/>
       <c r="G119" s="8"/>
-      <c r="H119" s="9"/>
-      <c r="I119" s="10"/>
-      <c r="J119" s="4"/>
-    </row>
-    <row r="120" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H119" s="5"/>
+      <c r="I119" s="9"/>
+      <c r="J119" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3"/>
-      <c r="B120" s="5"/>
-      <c r="C120" s="9"/>
+      <c r="B120" s="4"/>
+      <c r="C120" s="5"/>
       <c r="D120" s="6"/>
       <c r="E120" s="7"/>
       <c r="F120" s="8"/>
       <c r="G120" s="8"/>
-      <c r="H120" s="9"/>
-      <c r="I120" s="10"/>
-      <c r="J120" s="4"/>
-    </row>
-    <row r="121" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H120" s="5"/>
+      <c r="I120" s="9"/>
+      <c r="J120" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="3"/>
-      <c r="B121" s="5"/>
-      <c r="C121" s="9"/>
+      <c r="B121" s="4"/>
+      <c r="C121" s="5"/>
       <c r="D121" s="6"/>
       <c r="E121" s="7"/>
       <c r="F121" s="8"/>
       <c r="G121" s="8"/>
-      <c r="H121" s="9"/>
-      <c r="I121" s="10"/>
-      <c r="J121" s="4"/>
-    </row>
-    <row r="122" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H121" s="5"/>
+      <c r="I121" s="9"/>
+      <c r="J121" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="3"/>
-      <c r="B122" s="5"/>
-      <c r="C122" s="9"/>
+      <c r="B122" s="4"/>
+      <c r="C122" s="5"/>
       <c r="D122" s="6"/>
       <c r="E122" s="7"/>
       <c r="F122" s="8"/>
       <c r="G122" s="8"/>
-      <c r="H122" s="9"/>
-      <c r="I122" s="10"/>
-      <c r="J122" s="4"/>
-    </row>
-    <row r="123" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H122" s="5"/>
+      <c r="I122" s="9"/>
+      <c r="J122" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="3"/>
-      <c r="B123" s="5"/>
-      <c r="C123" s="9"/>
+      <c r="B123" s="4"/>
+      <c r="C123" s="5"/>
       <c r="D123" s="6"/>
       <c r="E123" s="7"/>
       <c r="F123" s="8"/>
       <c r="G123" s="8"/>
-      <c r="H123" s="9"/>
-      <c r="I123" s="10"/>
-      <c r="J123" s="4"/>
-    </row>
-    <row r="124" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H123" s="5"/>
+      <c r="I123" s="9"/>
+      <c r="J123" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="3"/>
-      <c r="B124" s="5"/>
-      <c r="C124" s="9"/>
+      <c r="B124" s="4"/>
+      <c r="C124" s="5"/>
       <c r="D124" s="6"/>
       <c r="E124" s="7"/>
       <c r="F124" s="8"/>
       <c r="G124" s="8"/>
-      <c r="H124" s="9"/>
-      <c r="I124" s="10"/>
-      <c r="J124" s="4"/>
-    </row>
-    <row r="125" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H124" s="5"/>
+      <c r="I124" s="9"/>
+      <c r="J124" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="3"/>
-      <c r="B125" s="5"/>
-      <c r="C125" s="9"/>
+      <c r="B125" s="4"/>
+      <c r="C125" s="5"/>
       <c r="D125" s="6"/>
       <c r="E125" s="7"/>
       <c r="F125" s="8"/>
       <c r="G125" s="8"/>
-      <c r="H125" s="9"/>
-      <c r="I125" s="10"/>
-      <c r="J125" s="4"/>
-    </row>
-    <row r="126" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H125" s="5"/>
+      <c r="I125" s="9"/>
+      <c r="J125" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="3"/>
-      <c r="B126" s="5"/>
-      <c r="C126" s="9"/>
+      <c r="B126" s="4"/>
+      <c r="C126" s="5"/>
       <c r="D126" s="6"/>
       <c r="E126" s="7"/>
       <c r="F126" s="8"/>
       <c r="G126" s="8"/>
-      <c r="H126" s="9"/>
-      <c r="I126" s="10"/>
-      <c r="J126" s="4"/>
-    </row>
-    <row r="127" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H126" s="5"/>
+      <c r="I126" s="9"/>
+      <c r="J126" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="3"/>
-      <c r="B127" s="5"/>
-      <c r="C127" s="9"/>
+      <c r="B127" s="4"/>
+      <c r="C127" s="5"/>
       <c r="D127" s="6"/>
       <c r="E127" s="7"/>
       <c r="F127" s="8"/>
       <c r="G127" s="8"/>
-      <c r="H127" s="9"/>
-      <c r="I127" s="10"/>
-      <c r="J127" s="4"/>
-    </row>
-    <row r="128" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H127" s="5"/>
+      <c r="I127" s="9"/>
+      <c r="J127" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="3"/>
-      <c r="B128" s="5"/>
-      <c r="C128" s="9"/>
+      <c r="B128" s="4"/>
+      <c r="C128" s="5"/>
       <c r="D128" s="6"/>
       <c r="E128" s="7"/>
       <c r="F128" s="8"/>
       <c r="G128" s="8"/>
-      <c r="H128" s="9"/>
-      <c r="I128" s="10"/>
-      <c r="J128" s="4"/>
-    </row>
-    <row r="129" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H128" s="5"/>
+      <c r="I128" s="9"/>
+      <c r="J128" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="3"/>
-      <c r="B129" s="5"/>
-      <c r="C129" s="9"/>
+      <c r="B129" s="4"/>
+      <c r="C129" s="5"/>
       <c r="D129" s="6"/>
       <c r="E129" s="7"/>
       <c r="F129" s="8"/>
       <c r="G129" s="8"/>
-      <c r="H129" s="9"/>
-      <c r="I129" s="10"/>
-      <c r="J129" s="4"/>
-    </row>
-    <row r="130" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H129" s="5"/>
+      <c r="I129" s="9"/>
+      <c r="J129" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="3"/>
-      <c r="B130" s="5"/>
-      <c r="C130" s="9"/>
+      <c r="B130" s="4"/>
+      <c r="C130" s="5"/>
       <c r="D130" s="6"/>
       <c r="E130" s="7"/>
       <c r="F130" s="8"/>
       <c r="G130" s="8"/>
-      <c r="H130" s="9"/>
-      <c r="I130" s="10"/>
-      <c r="J130" s="4"/>
-    </row>
-    <row r="131" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H130" s="5"/>
+      <c r="I130" s="9"/>
+      <c r="J130" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="3"/>
-      <c r="B131" s="5"/>
-      <c r="C131" s="9"/>
+      <c r="B131" s="4"/>
+      <c r="C131" s="5"/>
       <c r="D131" s="6"/>
       <c r="E131" s="7"/>
       <c r="F131" s="8"/>
       <c r="G131" s="8"/>
-      <c r="H131" s="9"/>
-      <c r="I131" s="10"/>
-      <c r="J131" s="4"/>
-    </row>
-    <row r="132" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H131" s="5"/>
+      <c r="I131" s="9"/>
+      <c r="J131" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="3"/>
-      <c r="B132" s="5"/>
-      <c r="C132" s="9"/>
+      <c r="B132" s="4"/>
+      <c r="C132" s="5"/>
       <c r="D132" s="6"/>
       <c r="E132" s="7"/>
       <c r="F132" s="8"/>
       <c r="G132" s="8"/>
-      <c r="H132" s="9"/>
-      <c r="I132" s="10"/>
-      <c r="J132" s="4"/>
-    </row>
-    <row r="133" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H132" s="5"/>
+      <c r="I132" s="9"/>
+      <c r="J132" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="3"/>
-      <c r="B133" s="5"/>
-      <c r="C133" s="9"/>
+      <c r="B133" s="4"/>
+      <c r="C133" s="5"/>
       <c r="D133" s="6"/>
       <c r="E133" s="7"/>
       <c r="F133" s="8"/>
       <c r="G133" s="8"/>
-      <c r="H133" s="9"/>
-      <c r="I133" s="10"/>
-      <c r="J133" s="4"/>
-    </row>
-    <row r="134" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H133" s="5"/>
+      <c r="I133" s="9"/>
+      <c r="J133" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="3"/>
-      <c r="B134" s="5"/>
-      <c r="C134" s="9"/>
+      <c r="B134" s="4"/>
+      <c r="C134" s="5"/>
       <c r="D134" s="6"/>
       <c r="E134" s="7"/>
       <c r="F134" s="8"/>
       <c r="G134" s="8"/>
-      <c r="H134" s="9"/>
-      <c r="I134" s="10"/>
-      <c r="J134" s="4"/>
-    </row>
-    <row r="135" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H134" s="5"/>
+      <c r="I134" s="9"/>
+      <c r="J134" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="3"/>
-      <c r="B135" s="5"/>
-      <c r="C135" s="9"/>
+      <c r="B135" s="4"/>
+      <c r="C135" s="5"/>
       <c r="D135" s="6"/>
       <c r="E135" s="7"/>
       <c r="F135" s="8"/>
       <c r="G135" s="8"/>
-      <c r="H135" s="9"/>
-      <c r="I135" s="10"/>
-      <c r="J135" s="4"/>
-    </row>
-    <row r="136" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H135" s="5"/>
+      <c r="I135" s="9"/>
+      <c r="J135" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="3"/>
-      <c r="B136" s="5"/>
-      <c r="C136" s="9"/>
+      <c r="B136" s="4"/>
+      <c r="C136" s="5"/>
       <c r="D136" s="6"/>
       <c r="E136" s="7"/>
       <c r="F136" s="8"/>
       <c r="G136" s="8"/>
-      <c r="H136" s="9"/>
-      <c r="I136" s="10"/>
-      <c r="J136" s="4"/>
-    </row>
-    <row r="137" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H136" s="5"/>
+      <c r="I136" s="9"/>
+      <c r="J136" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="3"/>
-      <c r="B137" s="5"/>
-      <c r="C137" s="9"/>
+      <c r="B137" s="4"/>
+      <c r="C137" s="5"/>
       <c r="D137" s="6"/>
       <c r="E137" s="7"/>
       <c r="F137" s="8"/>
       <c r="G137" s="8"/>
-      <c r="H137" s="9"/>
-      <c r="I137" s="10"/>
-      <c r="J137" s="4"/>
-    </row>
-    <row r="138" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H137" s="5"/>
+      <c r="I137" s="9"/>
+      <c r="J137" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="3"/>
-      <c r="B138" s="5"/>
-      <c r="C138" s="9"/>
+      <c r="B138" s="4"/>
+      <c r="C138" s="5"/>
       <c r="D138" s="6"/>
       <c r="E138" s="7"/>
       <c r="F138" s="8"/>
       <c r="G138" s="8"/>
-      <c r="H138" s="9"/>
-      <c r="I138" s="10"/>
-      <c r="J138" s="4"/>
-    </row>
-    <row r="139" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H138" s="5"/>
+      <c r="I138" s="9"/>
+      <c r="J138" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="3"/>
-      <c r="B139" s="5"/>
-      <c r="C139" s="9"/>
+      <c r="B139" s="4"/>
+      <c r="C139" s="5"/>
       <c r="D139" s="6"/>
       <c r="E139" s="7"/>
       <c r="F139" s="8"/>
       <c r="G139" s="8"/>
-      <c r="H139" s="9"/>
-      <c r="I139" s="10"/>
-      <c r="J139" s="4"/>
-    </row>
-    <row r="140" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H139" s="5"/>
+      <c r="I139" s="9"/>
+      <c r="J139" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="3"/>
-      <c r="B140" s="5"/>
-      <c r="C140" s="9"/>
+      <c r="B140" s="4"/>
+      <c r="C140" s="5"/>
       <c r="D140" s="6"/>
       <c r="E140" s="7"/>
       <c r="F140" s="8"/>
       <c r="G140" s="8"/>
-      <c r="H140" s="9"/>
-      <c r="I140" s="10"/>
-      <c r="J140" s="4"/>
-    </row>
-    <row r="141" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H140" s="5"/>
+      <c r="I140" s="9"/>
+      <c r="J140" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="3"/>
-      <c r="B141" s="5"/>
-      <c r="C141" s="9"/>
+      <c r="B141" s="4"/>
+      <c r="C141" s="5"/>
       <c r="D141" s="6"/>
       <c r="E141" s="7"/>
       <c r="F141" s="8"/>
       <c r="G141" s="8"/>
-      <c r="H141" s="9"/>
-      <c r="I141" s="10"/>
-      <c r="J141" s="4"/>
-    </row>
-    <row r="142" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H141" s="5"/>
+      <c r="I141" s="9"/>
+      <c r="J141" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="3"/>
-      <c r="B142" s="5"/>
-      <c r="C142" s="9"/>
+      <c r="B142" s="4"/>
+      <c r="C142" s="5"/>
       <c r="D142" s="6"/>
       <c r="E142" s="7"/>
       <c r="F142" s="8"/>
       <c r="G142" s="8"/>
-      <c r="H142" s="9"/>
-      <c r="I142" s="10"/>
-      <c r="J142" s="4"/>
-    </row>
-    <row r="143" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H142" s="5"/>
+      <c r="I142" s="9"/>
+      <c r="J142" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="3"/>
-      <c r="B143" s="5"/>
-      <c r="C143" s="9"/>
+      <c r="B143" s="4"/>
+      <c r="C143" s="5"/>
       <c r="D143" s="6"/>
       <c r="E143" s="7"/>
       <c r="F143" s="8"/>
       <c r="G143" s="8"/>
-      <c r="H143" s="9"/>
-      <c r="I143" s="10"/>
-      <c r="J143" s="4"/>
-    </row>
-    <row r="144" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H143" s="5"/>
+      <c r="I143" s="9"/>
+      <c r="J143" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="3"/>
-      <c r="B144" s="5"/>
-      <c r="C144" s="9"/>
+      <c r="B144" s="4"/>
+      <c r="C144" s="5"/>
       <c r="D144" s="6"/>
       <c r="E144" s="7"/>
       <c r="F144" s="8"/>
       <c r="G144" s="8"/>
-      <c r="H144" s="9"/>
-      <c r="I144" s="10"/>
-      <c r="J144" s="4"/>
-    </row>
-    <row r="145" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H144" s="5"/>
+      <c r="I144" s="9"/>
+      <c r="J144" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="3"/>
-      <c r="B145" s="5"/>
-      <c r="C145" s="9"/>
+      <c r="B145" s="4"/>
+      <c r="C145" s="5"/>
       <c r="D145" s="6"/>
       <c r="E145" s="7"/>
       <c r="F145" s="8"/>
       <c r="G145" s="8"/>
-      <c r="H145" s="9"/>
-      <c r="I145" s="10"/>
-      <c r="J145" s="4"/>
-    </row>
-    <row r="146" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H145" s="5"/>
+      <c r="I145" s="9"/>
+      <c r="J145" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="3"/>
-      <c r="B146" s="5"/>
-      <c r="C146" s="9"/>
+      <c r="B146" s="4"/>
+      <c r="C146" s="5"/>
       <c r="D146" s="6"/>
       <c r="E146" s="7"/>
       <c r="F146" s="8"/>
       <c r="G146" s="8"/>
-      <c r="H146" s="9"/>
-      <c r="I146" s="10"/>
-      <c r="J146" s="4"/>
-    </row>
-    <row r="147" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H146" s="5"/>
+      <c r="I146" s="9"/>
+      <c r="J146" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="3"/>
-      <c r="B147" s="5"/>
-      <c r="C147" s="9"/>
+      <c r="B147" s="4"/>
+      <c r="C147" s="5"/>
       <c r="D147" s="6"/>
       <c r="E147" s="7"/>
       <c r="F147" s="8"/>
       <c r="G147" s="8"/>
-      <c r="H147" s="9"/>
-      <c r="I147" s="10"/>
-      <c r="J147" s="4"/>
-    </row>
-    <row r="148" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H147" s="5"/>
+      <c r="I147" s="9"/>
+      <c r="J147" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="3"/>
-      <c r="B148" s="5"/>
-      <c r="C148" s="9"/>
+      <c r="B148" s="4"/>
+      <c r="C148" s="5"/>
       <c r="D148" s="6"/>
       <c r="E148" s="7"/>
       <c r="F148" s="8"/>
       <c r="G148" s="8"/>
-      <c r="H148" s="9"/>
-      <c r="I148" s="10"/>
-      <c r="J148" s="4"/>
-    </row>
-    <row r="149" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H148" s="5"/>
+      <c r="I148" s="9"/>
+      <c r="J148" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="3"/>
-      <c r="B149" s="5"/>
-      <c r="C149" s="9"/>
+      <c r="B149" s="4"/>
+      <c r="C149" s="5"/>
       <c r="D149" s="6"/>
       <c r="E149" s="7"/>
       <c r="F149" s="8"/>
       <c r="G149" s="8"/>
-      <c r="H149" s="9"/>
-      <c r="I149" s="10"/>
-      <c r="J149" s="4"/>
-    </row>
-    <row r="150" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H149" s="5"/>
+      <c r="I149" s="9"/>
+      <c r="J149" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="3"/>
-      <c r="B150" s="5"/>
-      <c r="C150" s="9"/>
+      <c r="B150" s="4"/>
+      <c r="C150" s="5"/>
       <c r="D150" s="6"/>
       <c r="E150" s="7"/>
       <c r="F150" s="8"/>
       <c r="G150" s="8"/>
-      <c r="H150" s="9"/>
-      <c r="I150" s="10"/>
-      <c r="J150" s="4"/>
-    </row>
-    <row r="151" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H150" s="5"/>
+      <c r="I150" s="9"/>
+      <c r="J150" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="3"/>
-      <c r="B151" s="5"/>
-      <c r="C151" s="9"/>
+      <c r="B151" s="4"/>
+      <c r="C151" s="5"/>
       <c r="D151" s="6"/>
       <c r="E151" s="7"/>
       <c r="F151" s="8"/>
       <c r="G151" s="8"/>
-      <c r="H151" s="9"/>
-      <c r="I151" s="10"/>
-      <c r="J151" s="4"/>
-    </row>
-    <row r="152" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H151" s="5"/>
+      <c r="I151" s="9"/>
+      <c r="J151" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="3"/>
-      <c r="B152" s="5"/>
-      <c r="C152" s="9"/>
+      <c r="B152" s="4"/>
+      <c r="C152" s="5"/>
       <c r="D152" s="6"/>
       <c r="E152" s="7"/>
       <c r="F152" s="8"/>
       <c r="G152" s="8"/>
-      <c r="H152" s="9"/>
-      <c r="I152" s="10"/>
-      <c r="J152" s="4"/>
-    </row>
-    <row r="153" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H152" s="5"/>
+      <c r="I152" s="9"/>
+      <c r="J152" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="3"/>
-      <c r="B153" s="5"/>
-      <c r="C153" s="9"/>
+      <c r="B153" s="4"/>
+      <c r="C153" s="5"/>
       <c r="D153" s="6"/>
       <c r="E153" s="7"/>
       <c r="F153" s="8"/>
       <c r="G153" s="8"/>
-      <c r="H153" s="9"/>
-      <c r="I153" s="10"/>
-      <c r="J153" s="4"/>
-    </row>
-    <row r="154" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H153" s="5"/>
+      <c r="I153" s="9"/>
+      <c r="J153" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="3"/>
-      <c r="B154" s="5"/>
-      <c r="C154" s="9"/>
+      <c r="B154" s="4"/>
+      <c r="C154" s="5"/>
       <c r="D154" s="6"/>
       <c r="E154" s="7"/>
       <c r="F154" s="8"/>
       <c r="G154" s="8"/>
-      <c r="H154" s="9"/>
-      <c r="I154" s="10"/>
-      <c r="J154" s="4"/>
-    </row>
-    <row r="155" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H154" s="5"/>
+      <c r="I154" s="9"/>
+      <c r="J154" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="3"/>
-      <c r="B155" s="5"/>
-      <c r="C155" s="9"/>
+      <c r="B155" s="4"/>
+      <c r="C155" s="5"/>
       <c r="D155" s="6"/>
       <c r="E155" s="7"/>
       <c r="F155" s="8"/>
       <c r="G155" s="8"/>
-      <c r="H155" s="9"/>
-      <c r="I155" s="10"/>
-      <c r="J155" s="4"/>
-    </row>
-    <row r="156" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H155" s="5"/>
+      <c r="I155" s="9"/>
+      <c r="J155" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="3"/>
-      <c r="B156" s="5"/>
-      <c r="C156" s="9"/>
+      <c r="B156" s="4"/>
+      <c r="C156" s="5"/>
       <c r="D156" s="6"/>
       <c r="E156" s="7"/>
       <c r="F156" s="8"/>
       <c r="G156" s="8"/>
-      <c r="H156" s="9"/>
-      <c r="I156" s="10"/>
-      <c r="J156" s="4"/>
-    </row>
-    <row r="157" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H156" s="5"/>
+      <c r="I156" s="9"/>
+      <c r="J156" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="3"/>
-      <c r="B157" s="5"/>
-      <c r="C157" s="9"/>
+      <c r="B157" s="4"/>
+      <c r="C157" s="5"/>
       <c r="D157" s="6"/>
       <c r="E157" s="7"/>
       <c r="F157" s="8"/>
       <c r="G157" s="8"/>
-      <c r="H157" s="9"/>
-      <c r="I157" s="10"/>
-      <c r="J157" s="4"/>
-    </row>
-    <row r="158" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H157" s="5"/>
+      <c r="I157" s="9"/>
+      <c r="J157" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="3"/>
-      <c r="B158" s="5"/>
-      <c r="C158" s="9"/>
+      <c r="B158" s="4"/>
+      <c r="C158" s="5"/>
       <c r="D158" s="6"/>
       <c r="E158" s="7"/>
       <c r="F158" s="8"/>
       <c r="G158" s="8"/>
-      <c r="H158" s="9"/>
-      <c r="I158" s="10"/>
-      <c r="J158" s="4"/>
-    </row>
-    <row r="159" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H158" s="5"/>
+      <c r="I158" s="9"/>
+      <c r="J158" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="3"/>
-      <c r="B159" s="5"/>
-      <c r="C159" s="9"/>
+      <c r="B159" s="4"/>
+      <c r="C159" s="5"/>
       <c r="D159" s="6"/>
       <c r="E159" s="7"/>
       <c r="F159" s="8"/>
       <c r="G159" s="8"/>
-      <c r="H159" s="9"/>
-      <c r="I159" s="10"/>
-      <c r="J159" s="4"/>
-    </row>
-    <row r="160" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H159" s="5"/>
+      <c r="I159" s="9"/>
+      <c r="J159" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="3"/>
-      <c r="B160" s="5"/>
-      <c r="C160" s="9"/>
+      <c r="B160" s="4"/>
+      <c r="C160" s="5"/>
       <c r="D160" s="6"/>
       <c r="E160" s="7"/>
       <c r="F160" s="8"/>
       <c r="G160" s="8"/>
-      <c r="H160" s="9"/>
-      <c r="I160" s="10"/>
-      <c r="J160" s="4"/>
-    </row>
-    <row r="161" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H160" s="5"/>
+      <c r="I160" s="9"/>
+      <c r="J160" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="3"/>
-      <c r="B161" s="5"/>
-      <c r="C161" s="9"/>
+      <c r="B161" s="4"/>
+      <c r="C161" s="5"/>
       <c r="D161" s="6"/>
       <c r="E161" s="7"/>
       <c r="F161" s="8"/>
       <c r="G161" s="8"/>
-      <c r="H161" s="9"/>
-      <c r="I161" s="10"/>
-      <c r="J161" s="4"/>
-    </row>
-    <row r="162" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H161" s="5"/>
+      <c r="I161" s="9"/>
+      <c r="J161" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="3"/>
-      <c r="B162" s="5"/>
-      <c r="C162" s="9"/>
+      <c r="B162" s="4"/>
+      <c r="C162" s="5"/>
       <c r="D162" s="6"/>
       <c r="E162" s="7"/>
       <c r="F162" s="8"/>
       <c r="G162" s="8"/>
-      <c r="H162" s="9"/>
-      <c r="I162" s="10"/>
-      <c r="J162" s="4"/>
-    </row>
-    <row r="163" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H162" s="5"/>
+      <c r="I162" s="9"/>
+      <c r="J162" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="3"/>
-      <c r="B163" s="5"/>
-      <c r="C163" s="9"/>
+      <c r="B163" s="4"/>
+      <c r="C163" s="5"/>
       <c r="D163" s="6"/>
       <c r="E163" s="7"/>
       <c r="F163" s="8"/>
       <c r="G163" s="8"/>
-      <c r="H163" s="9"/>
-      <c r="I163" s="10"/>
-      <c r="J163" s="4"/>
-    </row>
-    <row r="164" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H163" s="5"/>
+      <c r="I163" s="9"/>
+      <c r="J163" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="3"/>
-      <c r="B164" s="5"/>
-      <c r="C164" s="9"/>
+      <c r="B164" s="4"/>
+      <c r="C164" s="5"/>
       <c r="D164" s="6"/>
       <c r="E164" s="7"/>
       <c r="F164" s="8"/>
       <c r="G164" s="8"/>
-      <c r="H164" s="9"/>
-      <c r="I164" s="10"/>
-      <c r="J164" s="4"/>
-    </row>
-    <row r="165" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H164" s="5"/>
+      <c r="I164" s="9"/>
+      <c r="J164" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="3"/>
-      <c r="B165" s="5"/>
-      <c r="C165" s="9"/>
+      <c r="B165" s="4"/>
+      <c r="C165" s="5"/>
       <c r="D165" s="6"/>
       <c r="E165" s="7"/>
       <c r="F165" s="8"/>
       <c r="G165" s="8"/>
-      <c r="H165" s="9"/>
-      <c r="I165" s="10"/>
-      <c r="J165" s="4"/>
-    </row>
-    <row r="166" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H165" s="5"/>
+      <c r="I165" s="9"/>
+      <c r="J165" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="3"/>
-      <c r="B166" s="5"/>
-      <c r="C166" s="9"/>
+      <c r="B166" s="4"/>
+      <c r="C166" s="5"/>
       <c r="D166" s="6"/>
       <c r="E166" s="7"/>
       <c r="F166" s="8"/>
       <c r="G166" s="8"/>
-      <c r="H166" s="9"/>
-      <c r="I166" s="10"/>
-      <c r="J166" s="4"/>
-    </row>
-    <row r="167" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H166" s="5"/>
+      <c r="I166" s="9"/>
+      <c r="J166" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="3"/>
-      <c r="B167" s="5"/>
-      <c r="C167" s="9"/>
+      <c r="B167" s="4"/>
+      <c r="C167" s="5"/>
       <c r="D167" s="6"/>
       <c r="E167" s="7"/>
       <c r="F167" s="8"/>
       <c r="G167" s="8"/>
-      <c r="H167" s="9"/>
-      <c r="I167" s="10"/>
-      <c r="J167" s="4"/>
-    </row>
-    <row r="168" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H167" s="5"/>
+      <c r="I167" s="9"/>
+      <c r="J167" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="3"/>
-      <c r="B168" s="5"/>
-      <c r="C168" s="9"/>
+      <c r="B168" s="4"/>
+      <c r="C168" s="5"/>
       <c r="D168" s="6"/>
       <c r="E168" s="7"/>
       <c r="F168" s="8"/>
       <c r="G168" s="8"/>
-      <c r="H168" s="9"/>
-      <c r="I168" s="10"/>
-      <c r="J168" s="4"/>
-    </row>
-    <row r="169" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H168" s="5"/>
+      <c r="I168" s="9"/>
+      <c r="J168" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="3"/>
-      <c r="B169" s="5"/>
-      <c r="C169" s="9"/>
+      <c r="B169" s="4"/>
+      <c r="C169" s="5"/>
       <c r="D169" s="6"/>
       <c r="E169" s="7"/>
       <c r="F169" s="8"/>
       <c r="G169" s="8"/>
-      <c r="H169" s="9"/>
-      <c r="I169" s="10"/>
-      <c r="J169" s="4"/>
-    </row>
-    <row r="170" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H169" s="5"/>
+      <c r="I169" s="9"/>
+      <c r="J169" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="3"/>
-      <c r="B170" s="5"/>
-      <c r="C170" s="9"/>
+      <c r="B170" s="4"/>
+      <c r="C170" s="5"/>
       <c r="D170" s="6"/>
       <c r="E170" s="7"/>
       <c r="F170" s="8"/>
       <c r="G170" s="8"/>
-      <c r="H170" s="9"/>
-      <c r="I170" s="10"/>
-      <c r="J170" s="4"/>
-    </row>
-    <row r="171" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H170" s="5"/>
+      <c r="I170" s="9"/>
+      <c r="J170" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="3"/>
-      <c r="B171" s="5"/>
-      <c r="C171" s="9"/>
+      <c r="B171" s="4"/>
+      <c r="C171" s="5"/>
       <c r="D171" s="6"/>
       <c r="E171" s="7"/>
       <c r="F171" s="8"/>
       <c r="G171" s="8"/>
-      <c r="H171" s="9"/>
-      <c r="I171" s="10"/>
-      <c r="J171" s="4"/>
-    </row>
-    <row r="172" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H171" s="5"/>
+      <c r="I171" s="9"/>
+      <c r="J171" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="3"/>
-      <c r="B172" s="5"/>
-      <c r="C172" s="9"/>
+      <c r="B172" s="4"/>
+      <c r="C172" s="5"/>
       <c r="D172" s="6"/>
       <c r="E172" s="7"/>
       <c r="F172" s="8"/>
       <c r="G172" s="8"/>
-      <c r="H172" s="9"/>
-      <c r="I172" s="10"/>
-      <c r="J172" s="4"/>
-    </row>
-    <row r="173" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H172" s="5"/>
+      <c r="I172" s="9"/>
+      <c r="J172" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="3"/>
-      <c r="B173" s="5"/>
-      <c r="C173" s="9"/>
+      <c r="B173" s="4"/>
+      <c r="C173" s="5"/>
       <c r="D173" s="6"/>
       <c r="E173" s="7"/>
       <c r="F173" s="8"/>
       <c r="G173" s="8"/>
-      <c r="H173" s="9"/>
-      <c r="I173" s="10"/>
-      <c r="J173" s="4"/>
-    </row>
-    <row r="174" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H173" s="5"/>
+      <c r="I173" s="9"/>
+      <c r="J173" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="3"/>
-      <c r="B174" s="5"/>
-      <c r="C174" s="9"/>
+      <c r="B174" s="4"/>
+      <c r="C174" s="5"/>
       <c r="D174" s="6"/>
       <c r="E174" s="7"/>
       <c r="F174" s="8"/>
       <c r="G174" s="8"/>
-      <c r="H174" s="9"/>
-      <c r="I174" s="10"/>
-      <c r="J174" s="4"/>
-    </row>
-    <row r="175" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H174" s="5"/>
+      <c r="I174" s="9"/>
+      <c r="J174" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="3"/>
-      <c r="B175" s="5"/>
-      <c r="C175" s="9"/>
+      <c r="B175" s="4"/>
+      <c r="C175" s="5"/>
       <c r="D175" s="6"/>
       <c r="E175" s="7"/>
       <c r="F175" s="8"/>
       <c r="G175" s="8"/>
-      <c r="H175" s="9"/>
-      <c r="I175" s="10"/>
-      <c r="J175" s="4"/>
-    </row>
-    <row r="176" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H175" s="5"/>
+      <c r="I175" s="9"/>
+      <c r="J175" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="3"/>
-      <c r="B176" s="5"/>
-      <c r="C176" s="9"/>
+      <c r="B176" s="4"/>
+      <c r="C176" s="5"/>
       <c r="D176" s="6"/>
       <c r="E176" s="7"/>
       <c r="F176" s="8"/>
       <c r="G176" s="8"/>
-      <c r="H176" s="9"/>
-      <c r="I176" s="10"/>
-      <c r="J176" s="4"/>
-    </row>
-    <row r="177" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H176" s="5"/>
+      <c r="I176" s="9"/>
+      <c r="J176" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="3"/>
-      <c r="B177" s="5"/>
-      <c r="C177" s="9"/>
+      <c r="B177" s="4"/>
+      <c r="C177" s="5"/>
       <c r="D177" s="6"/>
       <c r="E177" s="7"/>
       <c r="F177" s="8"/>
       <c r="G177" s="8"/>
-      <c r="H177" s="9"/>
-      <c r="I177" s="10"/>
-      <c r="J177" s="4"/>
-    </row>
-    <row r="178" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H177" s="5"/>
+      <c r="I177" s="9"/>
+      <c r="J177" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="3"/>
-      <c r="B178" s="5"/>
-      <c r="C178" s="9"/>
+      <c r="B178" s="4"/>
+      <c r="C178" s="5"/>
       <c r="D178" s="6"/>
       <c r="E178" s="7"/>
       <c r="F178" s="8"/>
       <c r="G178" s="8"/>
-      <c r="H178" s="9"/>
-      <c r="I178" s="10"/>
-      <c r="J178" s="4"/>
-    </row>
-    <row r="179" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H178" s="5"/>
+      <c r="I178" s="9"/>
+      <c r="J178" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="3"/>
-      <c r="B179" s="5"/>
-      <c r="C179" s="9"/>
+      <c r="B179" s="4"/>
+      <c r="C179" s="5"/>
       <c r="D179" s="6"/>
       <c r="E179" s="7"/>
       <c r="F179" s="8"/>
       <c r="G179" s="8"/>
-      <c r="H179" s="9"/>
-      <c r="I179" s="10"/>
-      <c r="J179" s="4"/>
-    </row>
-    <row r="180" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H179" s="5"/>
+      <c r="I179" s="9"/>
+      <c r="J179" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="3"/>
-      <c r="B180" s="5"/>
-      <c r="C180" s="9"/>
+      <c r="B180" s="4"/>
+      <c r="C180" s="5"/>
       <c r="D180" s="6"/>
       <c r="E180" s="7"/>
       <c r="F180" s="8"/>
       <c r="G180" s="8"/>
-      <c r="H180" s="9"/>
-      <c r="I180" s="10"/>
-      <c r="J180" s="4"/>
-    </row>
-    <row r="181" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H180" s="5"/>
+      <c r="I180" s="9"/>
+      <c r="J180" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="3"/>
-      <c r="B181" s="5"/>
-      <c r="C181" s="9"/>
+      <c r="B181" s="4"/>
+      <c r="C181" s="5"/>
       <c r="D181" s="6"/>
       <c r="E181" s="7"/>
       <c r="F181" s="8"/>
       <c r="G181" s="8"/>
-      <c r="H181" s="9"/>
-      <c r="I181" s="10"/>
-      <c r="J181" s="4"/>
-    </row>
-    <row r="182" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H181" s="5"/>
+      <c r="I181" s="9"/>
+      <c r="J181" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="3"/>
-      <c r="B182" s="5"/>
-      <c r="C182" s="9"/>
+      <c r="B182" s="4"/>
+      <c r="C182" s="5"/>
       <c r="D182" s="6"/>
       <c r="E182" s="7"/>
       <c r="F182" s="8"/>
       <c r="G182" s="8"/>
-      <c r="H182" s="9"/>
-      <c r="I182" s="10"/>
-      <c r="J182" s="4"/>
-    </row>
-    <row r="183" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H182" s="5"/>
+      <c r="I182" s="9"/>
+      <c r="J182" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="3"/>
-      <c r="B183" s="5"/>
-      <c r="C183" s="9"/>
+      <c r="B183" s="4"/>
+      <c r="C183" s="5"/>
       <c r="D183" s="6"/>
       <c r="E183" s="7"/>
       <c r="F183" s="8"/>
       <c r="G183" s="8"/>
-      <c r="H183" s="9"/>
-      <c r="I183" s="10"/>
-      <c r="J183" s="4"/>
-    </row>
-    <row r="184" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H183" s="5"/>
+      <c r="I183" s="9"/>
+      <c r="J183" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="3"/>
-      <c r="B184" s="5"/>
-      <c r="C184" s="9"/>
+      <c r="B184" s="4"/>
+      <c r="C184" s="5"/>
       <c r="D184" s="6"/>
       <c r="E184" s="7"/>
       <c r="F184" s="8"/>
       <c r="G184" s="8"/>
-      <c r="H184" s="9"/>
-      <c r="I184" s="10"/>
-      <c r="J184" s="4"/>
-    </row>
-    <row r="185" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H184" s="5"/>
+      <c r="I184" s="9"/>
+      <c r="J184" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="3"/>
-      <c r="B185" s="5"/>
-      <c r="C185" s="9"/>
+      <c r="B185" s="4"/>
+      <c r="C185" s="5"/>
       <c r="D185" s="6"/>
       <c r="E185" s="7"/>
       <c r="F185" s="8"/>
       <c r="G185" s="8"/>
-      <c r="H185" s="9"/>
-      <c r="I185" s="10"/>
-      <c r="J185" s="4"/>
-    </row>
-    <row r="186" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H185" s="5"/>
+      <c r="I185" s="9"/>
+      <c r="J185" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="3"/>
-      <c r="B186" s="5"/>
-      <c r="C186" s="9"/>
+      <c r="B186" s="4"/>
+      <c r="C186" s="5"/>
       <c r="D186" s="6"/>
       <c r="E186" s="7"/>
       <c r="F186" s="8"/>
       <c r="G186" s="8"/>
-      <c r="H186" s="9"/>
-      <c r="I186" s="10"/>
-      <c r="J186" s="4"/>
-    </row>
-    <row r="187" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H186" s="5"/>
+      <c r="I186" s="9"/>
+      <c r="J186" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="3"/>
-      <c r="B187" s="5"/>
-      <c r="C187" s="9"/>
+      <c r="B187" s="4"/>
+      <c r="C187" s="5"/>
       <c r="D187" s="6"/>
       <c r="E187" s="7"/>
       <c r="F187" s="8"/>
       <c r="G187" s="8"/>
-      <c r="H187" s="9"/>
-      <c r="I187" s="10"/>
-      <c r="J187" s="4"/>
-    </row>
-    <row r="188" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H187" s="5"/>
+      <c r="I187" s="9"/>
+      <c r="J187" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="3"/>
-      <c r="B188" s="5"/>
-      <c r="C188" s="9"/>
+      <c r="B188" s="4"/>
+      <c r="C188" s="5"/>
       <c r="D188" s="6"/>
       <c r="E188" s="7"/>
       <c r="F188" s="8"/>
       <c r="G188" s="8"/>
-      <c r="H188" s="9"/>
-      <c r="I188" s="10"/>
-      <c r="J188" s="4"/>
-    </row>
-    <row r="189" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H188" s="5"/>
+      <c r="I188" s="9"/>
+      <c r="J188" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="3"/>
-      <c r="B189" s="5"/>
-      <c r="C189" s="9"/>
+      <c r="B189" s="4"/>
+      <c r="C189" s="5"/>
       <c r="D189" s="6"/>
       <c r="E189" s="7"/>
       <c r="F189" s="8"/>
       <c r="G189" s="8"/>
-      <c r="H189" s="9"/>
-      <c r="I189" s="10"/>
-      <c r="J189" s="4"/>
-    </row>
-    <row r="190" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H189" s="5"/>
+      <c r="I189" s="9"/>
+      <c r="J189" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="3"/>
-      <c r="B190" s="5"/>
-      <c r="C190" s="9"/>
+      <c r="B190" s="4"/>
+      <c r="C190" s="5"/>
       <c r="D190" s="6"/>
       <c r="E190" s="7"/>
       <c r="F190" s="8"/>
       <c r="G190" s="8"/>
-      <c r="H190" s="9"/>
-      <c r="I190" s="10"/>
-      <c r="J190" s="4"/>
-    </row>
-    <row r="191" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H190" s="5"/>
+      <c r="I190" s="9"/>
+      <c r="J190" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="3"/>
-      <c r="B191" s="5"/>
-      <c r="C191" s="9"/>
+      <c r="B191" s="4"/>
+      <c r="C191" s="5"/>
       <c r="D191" s="6"/>
       <c r="E191" s="7"/>
       <c r="F191" s="8"/>
       <c r="G191" s="8"/>
-      <c r="H191" s="9"/>
-      <c r="I191" s="10"/>
-      <c r="J191" s="4"/>
-    </row>
-    <row r="192" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H191" s="5"/>
+      <c r="I191" s="9"/>
+      <c r="J191" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="3"/>
-      <c r="B192" s="5"/>
-      <c r="C192" s="9"/>
+      <c r="B192" s="4"/>
+      <c r="C192" s="5"/>
       <c r="D192" s="6"/>
       <c r="E192" s="7"/>
       <c r="F192" s="8"/>
       <c r="G192" s="8"/>
-      <c r="H192" s="9"/>
-      <c r="I192" s="10"/>
-      <c r="J192" s="4"/>
-    </row>
-    <row r="193" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H192" s="5"/>
+      <c r="I192" s="9"/>
+      <c r="J192" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="3"/>
-      <c r="B193" s="5"/>
-      <c r="C193" s="9"/>
+      <c r="B193" s="4"/>
+      <c r="C193" s="5"/>
       <c r="D193" s="6"/>
       <c r="E193" s="7"/>
       <c r="F193" s="8"/>
       <c r="G193" s="8"/>
-      <c r="H193" s="9"/>
-      <c r="I193" s="10"/>
-      <c r="J193" s="4"/>
-    </row>
-    <row r="194" spans="1:10" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H193" s="5"/>
+      <c r="I193" s="9"/>
+      <c r="J193" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="3"/>
-      <c r="B194" s="5"/>
-      <c r="C194" s="9"/>
+      <c r="B194" s="4"/>
+      <c r="C194" s="5"/>
       <c r="D194" s="6"/>
       <c r="E194" s="7"/>
       <c r="F194" s="8"/>
       <c r="G194" s="8"/>
-      <c r="H194" s="9"/>
-      <c r="I194" s="10"/>
-      <c r="J194" s="4"/>
+      <c r="H194" s="5"/>
+      <c r="I194" s="9"/>
+      <c r="J194" s="10" t="e">
+        <f>Table2[[#This Row],[Livrés]]/Table2[[#This Row],[T.Colis]]</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dummy-content/MARJANE-MALL-EXPORT-DATA.xlsx
+++ b/dummy-content/MARJANE-MALL-EXPORT-DATA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UNK\Desktop\GoFleet-Enhancer\dummy-content\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User1\Desktop\GoFleet-Enhancer\dummy-content\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B429A02-3AE0-457C-8943-853C184D8995}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A89541-5500-4E93-B3DC-600AABDE9ED1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23250" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -88,7 +88,7 @@
     </font>
     <font>
       <sz val="12"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -184,7 +184,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -214,6 +214,7 @@
     <xf numFmtId="164" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -228,7 +229,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -249,7 +250,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -283,7 +284,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -318,7 +319,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -353,7 +354,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -388,7 +389,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -423,7 +424,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -458,7 +459,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -493,7 +494,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -528,7 +529,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -563,7 +564,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color theme="0"/>
+        <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -622,72 +623,6 @@
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
     <mruColors>
       <color rgb="FFAEFEFC"/>
       <color rgb="FFFFAFAF"/>
@@ -730,10 +665,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="D8DEE9"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="2E3440"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -988,15 +923,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J194"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J196"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="40.140625" style="1" customWidth="1"/>
-    <col min="2" max="10" width="18.85546875" style="1" customWidth="1"/>
-    <col min="11" max="25" width="18.85546875" customWidth="1"/>
+    <col min="1" max="1" width="40.1796875" style="1" customWidth="1"/>
+    <col min="2" max="10" width="18.81640625" style="1" customWidth="1"/>
+    <col min="11" max="25" width="18.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1028,7 +963,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
       <c r="B2" s="4"/>
       <c r="C2" s="5"/>
@@ -1043,7 +978,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="4"/>
       <c r="C3" s="5"/>
@@ -1058,7 +993,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3"/>
       <c r="B4" s="4"/>
       <c r="C4" s="5"/>
@@ -1073,7 +1008,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3"/>
       <c r="B5" s="4"/>
       <c r="C5" s="5"/>
@@ -1088,7 +1023,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
@@ -1103,7 +1038,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="4"/>
       <c r="C7" s="5"/>
@@ -1118,7 +1053,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" s="4"/>
       <c r="C8" s="5"/>
@@ -1133,7 +1068,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="4"/>
       <c r="C9" s="5"/>
@@ -1148,7 +1083,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="4"/>
       <c r="C10" s="5"/>
@@ -1163,7 +1098,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="4"/>
       <c r="C11" s="5"/>
@@ -1178,7 +1113,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
       <c r="B12" s="4"/>
       <c r="C12" s="5"/>
@@ -1193,7 +1128,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
       <c r="B13" s="4"/>
       <c r="C13" s="5"/>
@@ -1208,7 +1143,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
       <c r="B14" s="4"/>
       <c r="C14" s="5"/>
@@ -1223,7 +1158,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
       <c r="B15" s="4"/>
       <c r="C15" s="5"/>
@@ -1238,7 +1173,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3"/>
       <c r="B16" s="4"/>
       <c r="C16" s="5"/>
@@ -1253,7 +1188,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
       <c r="B17" s="4"/>
       <c r="C17" s="5"/>
@@ -1268,7 +1203,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
       <c r="B18" s="4"/>
       <c r="C18" s="5"/>
@@ -1283,7 +1218,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3"/>
       <c r="B19" s="4"/>
       <c r="C19" s="5"/>
@@ -1298,7 +1233,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3"/>
       <c r="B20" s="4"/>
       <c r="C20" s="5"/>
@@ -1313,7 +1248,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3"/>
       <c r="B21" s="4"/>
       <c r="C21" s="5"/>
@@ -1328,7 +1263,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3"/>
       <c r="B22" s="4"/>
       <c r="C22" s="5"/>
@@ -1343,7 +1278,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3"/>
       <c r="B23" s="4"/>
       <c r="C23" s="5"/>
@@ -1358,7 +1293,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3"/>
       <c r="B24" s="4"/>
       <c r="C24" s="5"/>
@@ -1373,7 +1308,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3"/>
       <c r="B25" s="4"/>
       <c r="C25" s="5"/>
@@ -1388,7 +1323,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3"/>
       <c r="B26" s="4"/>
       <c r="C26" s="5"/>
@@ -1403,7 +1338,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>
       <c r="B27" s="4"/>
       <c r="C27" s="5"/>
@@ -1418,7 +1353,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3"/>
       <c r="B28" s="4"/>
       <c r="C28" s="5"/>
@@ -1433,7 +1368,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3"/>
       <c r="B29" s="4"/>
       <c r="C29" s="5"/>
@@ -1448,7 +1383,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3"/>
       <c r="B30" s="4"/>
       <c r="C30" s="5"/>
@@ -1463,7 +1398,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3"/>
       <c r="B31" s="4"/>
       <c r="C31" s="5"/>
@@ -1478,7 +1413,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3"/>
       <c r="B32" s="4"/>
       <c r="C32" s="5"/>
@@ -1493,7 +1428,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3"/>
       <c r="B33" s="4"/>
       <c r="C33" s="5"/>
@@ -1508,7 +1443,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3"/>
       <c r="B34" s="4"/>
       <c r="C34" s="5"/>
@@ -1523,7 +1458,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3"/>
       <c r="B35" s="4"/>
       <c r="C35" s="5"/>
@@ -1538,7 +1473,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3"/>
       <c r="B36" s="4"/>
       <c r="C36" s="5"/>
@@ -1553,7 +1488,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3"/>
       <c r="B37" s="4"/>
       <c r="C37" s="5"/>
@@ -1568,7 +1503,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3"/>
       <c r="B38" s="4"/>
       <c r="C38" s="5"/>
@@ -1583,7 +1518,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3"/>
       <c r="B39" s="4"/>
       <c r="C39" s="5"/>
@@ -1598,7 +1533,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3"/>
       <c r="B40" s="4"/>
       <c r="C40" s="5"/>
@@ -1613,7 +1548,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3"/>
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
@@ -1628,7 +1563,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3"/>
       <c r="B42" s="4"/>
       <c r="C42" s="5"/>
@@ -1643,7 +1578,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3"/>
       <c r="B43" s="4"/>
       <c r="C43" s="5"/>
@@ -1658,7 +1593,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3"/>
       <c r="B44" s="4"/>
       <c r="C44" s="5"/>
@@ -1673,7 +1608,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3"/>
       <c r="B45" s="4"/>
       <c r="C45" s="5"/>
@@ -1688,7 +1623,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3"/>
       <c r="B46" s="4"/>
       <c r="C46" s="5"/>
@@ -1703,7 +1638,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3"/>
       <c r="B47" s="4"/>
       <c r="C47" s="5"/>
@@ -1718,7 +1653,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="3"/>
       <c r="B48" s="4"/>
       <c r="C48" s="5"/>
@@ -1733,7 +1668,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3"/>
       <c r="B49" s="4"/>
       <c r="C49" s="5"/>
@@ -1748,7 +1683,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="3"/>
       <c r="B50" s="4"/>
       <c r="C50" s="5"/>
@@ -1763,7 +1698,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3"/>
       <c r="B51" s="4"/>
       <c r="C51" s="5"/>
@@ -1778,7 +1713,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="3"/>
       <c r="B52" s="4"/>
       <c r="C52" s="5"/>
@@ -1793,7 +1728,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3"/>
       <c r="B53" s="4"/>
       <c r="C53" s="5"/>
@@ -1808,7 +1743,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="3"/>
       <c r="B54" s="4"/>
       <c r="C54" s="5"/>
@@ -1823,7 +1758,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="3"/>
       <c r="B55" s="4"/>
       <c r="C55" s="5"/>
@@ -1838,7 +1773,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="3"/>
       <c r="B56" s="4"/>
       <c r="C56" s="5"/>
@@ -1853,7 +1788,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="3"/>
       <c r="B57" s="4"/>
       <c r="C57" s="5"/>
@@ -1868,7 +1803,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="3"/>
       <c r="B58" s="4"/>
       <c r="C58" s="5"/>
@@ -1883,7 +1818,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="3"/>
       <c r="B59" s="4"/>
       <c r="C59" s="5"/>
@@ -1898,7 +1833,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="3"/>
       <c r="B60" s="4"/>
       <c r="C60" s="5"/>
@@ -1913,7 +1848,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="3"/>
       <c r="B61" s="4"/>
       <c r="C61" s="5"/>
@@ -1928,7 +1863,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="3"/>
       <c r="B62" s="4"/>
       <c r="C62" s="5"/>
@@ -1943,7 +1878,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="3"/>
       <c r="B63" s="4"/>
       <c r="C63" s="5"/>
@@ -1958,7 +1893,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="3"/>
       <c r="B64" s="4"/>
       <c r="C64" s="5"/>
@@ -1973,7 +1908,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="3"/>
       <c r="B65" s="4"/>
       <c r="C65" s="5"/>
@@ -1988,7 +1923,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="3"/>
       <c r="B66" s="4"/>
       <c r="C66" s="5"/>
@@ -2003,7 +1938,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="3"/>
       <c r="B67" s="4"/>
       <c r="C67" s="5"/>
@@ -2018,7 +1953,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="3"/>
       <c r="B68" s="4"/>
       <c r="C68" s="5"/>
@@ -2033,7 +1968,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="3"/>
       <c r="B69" s="4"/>
       <c r="C69" s="5"/>
@@ -2048,7 +1983,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="3"/>
       <c r="B70" s="4"/>
       <c r="C70" s="5"/>
@@ -2063,7 +1998,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="3"/>
       <c r="B71" s="4"/>
       <c r="C71" s="5"/>
@@ -2078,7 +2013,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="3"/>
       <c r="B72" s="4"/>
       <c r="C72" s="5"/>
@@ -2093,7 +2028,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="3"/>
       <c r="B73" s="4"/>
       <c r="C73" s="5"/>
@@ -2108,7 +2043,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="3"/>
       <c r="B74" s="4"/>
       <c r="C74" s="5"/>
@@ -2123,7 +2058,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="3"/>
       <c r="B75" s="4"/>
       <c r="C75" s="5"/>
@@ -2138,7 +2073,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="3"/>
       <c r="B76" s="4"/>
       <c r="C76" s="5"/>
@@ -2153,7 +2088,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="3"/>
       <c r="B77" s="4"/>
       <c r="C77" s="5"/>
@@ -2168,7 +2103,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="3"/>
       <c r="B78" s="4"/>
       <c r="C78" s="5"/>
@@ -2183,7 +2118,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="3"/>
       <c r="B79" s="4"/>
       <c r="C79" s="5"/>
@@ -2198,7 +2133,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="3"/>
       <c r="B80" s="4"/>
       <c r="C80" s="5"/>
@@ -2213,7 +2148,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="3"/>
       <c r="B81" s="4"/>
       <c r="C81" s="5"/>
@@ -2228,7 +2163,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="3"/>
       <c r="B82" s="4"/>
       <c r="C82" s="5"/>
@@ -2243,7 +2178,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="3"/>
       <c r="B83" s="4"/>
       <c r="C83" s="5"/>
@@ -2258,7 +2193,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="3"/>
       <c r="B84" s="4"/>
       <c r="C84" s="5"/>
@@ -2273,7 +2208,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="3"/>
       <c r="B85" s="4"/>
       <c r="C85" s="5"/>
@@ -2288,7 +2223,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="3"/>
       <c r="B86" s="4"/>
       <c r="C86" s="5"/>
@@ -2303,7 +2238,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="3"/>
       <c r="B87" s="4"/>
       <c r="C87" s="5"/>
@@ -2318,7 +2253,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="3"/>
       <c r="B88" s="4"/>
       <c r="C88" s="5"/>
@@ -2333,7 +2268,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="3"/>
       <c r="B89" s="4"/>
       <c r="C89" s="5"/>
@@ -2348,7 +2283,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="3"/>
       <c r="B90" s="4"/>
       <c r="C90" s="5"/>
@@ -2363,7 +2298,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="3"/>
       <c r="B91" s="4"/>
       <c r="C91" s="5"/>
@@ -2378,7 +2313,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="3"/>
       <c r="B92" s="4"/>
       <c r="C92" s="5"/>
@@ -2393,7 +2328,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="3"/>
       <c r="B93" s="4"/>
       <c r="C93" s="5"/>
@@ -2408,7 +2343,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="3"/>
       <c r="B94" s="4"/>
       <c r="C94" s="5"/>
@@ -2423,7 +2358,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="3"/>
       <c r="B95" s="4"/>
       <c r="C95" s="5"/>
@@ -2438,7 +2373,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="3"/>
       <c r="B96" s="4"/>
       <c r="C96" s="5"/>
@@ -2453,7 +2388,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="3"/>
       <c r="B97" s="4"/>
       <c r="C97" s="5"/>
@@ -2468,7 +2403,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="3"/>
       <c r="B98" s="4"/>
       <c r="C98" s="5"/>
@@ -2483,7 +2418,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="3"/>
       <c r="B99" s="4"/>
       <c r="C99" s="5"/>
@@ -2498,7 +2433,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="3"/>
       <c r="B100" s="4"/>
       <c r="C100" s="5"/>
@@ -2513,7 +2448,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="3"/>
       <c r="B101" s="4"/>
       <c r="C101" s="5"/>
@@ -2528,7 +2463,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="3"/>
       <c r="B102" s="4"/>
       <c r="C102" s="5"/>
@@ -2543,7 +2478,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="3"/>
       <c r="B103" s="4"/>
       <c r="C103" s="5"/>
@@ -2558,7 +2493,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="3"/>
       <c r="B104" s="4"/>
       <c r="C104" s="5"/>
@@ -2573,7 +2508,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="3"/>
       <c r="B105" s="4"/>
       <c r="C105" s="5"/>
@@ -2588,7 +2523,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="3"/>
       <c r="B106" s="4"/>
       <c r="C106" s="5"/>
@@ -2603,7 +2538,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="3"/>
       <c r="B107" s="4"/>
       <c r="C107" s="5"/>
@@ -2618,7 +2553,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="3"/>
       <c r="B108" s="4"/>
       <c r="C108" s="5"/>
@@ -2633,7 +2568,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="3"/>
       <c r="B109" s="4"/>
       <c r="C109" s="5"/>
@@ -2648,7 +2583,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="3"/>
       <c r="B110" s="4"/>
       <c r="C110" s="5"/>
@@ -2663,7 +2598,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="3"/>
       <c r="B111" s="4"/>
       <c r="C111" s="5"/>
@@ -2678,7 +2613,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="3"/>
       <c r="B112" s="4"/>
       <c r="C112" s="5"/>
@@ -2693,7 +2628,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="3"/>
       <c r="B113" s="4"/>
       <c r="C113" s="5"/>
@@ -2708,7 +2643,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="3"/>
       <c r="B114" s="4"/>
       <c r="C114" s="5"/>
@@ -2723,7 +2658,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="3"/>
       <c r="B115" s="4"/>
       <c r="C115" s="5"/>
@@ -2738,7 +2673,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="3"/>
       <c r="B116" s="4"/>
       <c r="C116" s="5"/>
@@ -2753,7 +2688,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="3"/>
       <c r="B117" s="4"/>
       <c r="C117" s="5"/>
@@ -2768,7 +2703,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="3"/>
       <c r="B118" s="4"/>
       <c r="C118" s="5"/>
@@ -2783,7 +2718,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="3"/>
       <c r="B119" s="4"/>
       <c r="C119" s="5"/>
@@ -2798,7 +2733,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="3"/>
       <c r="B120" s="4"/>
       <c r="C120" s="5"/>
@@ -2813,7 +2748,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="3"/>
       <c r="B121" s="4"/>
       <c r="C121" s="5"/>
@@ -2828,7 +2763,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="3"/>
       <c r="B122" s="4"/>
       <c r="C122" s="5"/>
@@ -2843,7 +2778,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="3"/>
       <c r="B123" s="4"/>
       <c r="C123" s="5"/>
@@ -2858,7 +2793,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="3"/>
       <c r="B124" s="4"/>
       <c r="C124" s="5"/>
@@ -2873,7 +2808,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="3"/>
       <c r="B125" s="4"/>
       <c r="C125" s="5"/>
@@ -2888,7 +2823,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="3"/>
       <c r="B126" s="4"/>
       <c r="C126" s="5"/>
@@ -2903,7 +2838,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="3"/>
       <c r="B127" s="4"/>
       <c r="C127" s="5"/>
@@ -2918,7 +2853,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="3"/>
       <c r="B128" s="4"/>
       <c r="C128" s="5"/>
@@ -2933,7 +2868,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="3"/>
       <c r="B129" s="4"/>
       <c r="C129" s="5"/>
@@ -2948,7 +2883,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="3"/>
       <c r="B130" s="4"/>
       <c r="C130" s="5"/>
@@ -2963,7 +2898,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="3"/>
       <c r="B131" s="4"/>
       <c r="C131" s="5"/>
@@ -2978,7 +2913,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="3"/>
       <c r="B132" s="4"/>
       <c r="C132" s="5"/>
@@ -2993,7 +2928,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="3"/>
       <c r="B133" s="4"/>
       <c r="C133" s="5"/>
@@ -3008,7 +2943,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="3"/>
       <c r="B134" s="4"/>
       <c r="C134" s="5"/>
@@ -3023,7 +2958,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="3"/>
       <c r="B135" s="4"/>
       <c r="C135" s="5"/>
@@ -3038,7 +2973,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="3"/>
       <c r="B136" s="4"/>
       <c r="C136" s="5"/>
@@ -3053,7 +2988,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="3"/>
       <c r="B137" s="4"/>
       <c r="C137" s="5"/>
@@ -3068,7 +3003,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="3"/>
       <c r="B138" s="4"/>
       <c r="C138" s="5"/>
@@ -3083,7 +3018,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="3"/>
       <c r="B139" s="4"/>
       <c r="C139" s="5"/>
@@ -3098,7 +3033,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="3"/>
       <c r="B140" s="4"/>
       <c r="C140" s="5"/>
@@ -3113,7 +3048,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="3"/>
       <c r="B141" s="4"/>
       <c r="C141" s="5"/>
@@ -3128,7 +3063,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="3"/>
       <c r="B142" s="4"/>
       <c r="C142" s="5"/>
@@ -3143,7 +3078,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="3"/>
       <c r="B143" s="4"/>
       <c r="C143" s="5"/>
@@ -3158,7 +3093,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="3"/>
       <c r="B144" s="4"/>
       <c r="C144" s="5"/>
@@ -3173,7 +3108,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="3"/>
       <c r="B145" s="4"/>
       <c r="C145" s="5"/>
@@ -3188,7 +3123,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="3"/>
       <c r="B146" s="4"/>
       <c r="C146" s="5"/>
@@ -3203,7 +3138,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="3"/>
       <c r="B147" s="4"/>
       <c r="C147" s="5"/>
@@ -3218,7 +3153,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="3"/>
       <c r="B148" s="4"/>
       <c r="C148" s="5"/>
@@ -3233,7 +3168,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="3"/>
       <c r="B149" s="4"/>
       <c r="C149" s="5"/>
@@ -3248,7 +3183,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="3"/>
       <c r="B150" s="4"/>
       <c r="C150" s="5"/>
@@ -3263,7 +3198,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="151" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="3"/>
       <c r="B151" s="4"/>
       <c r="C151" s="5"/>
@@ -3278,7 +3213,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="152" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="3"/>
       <c r="B152" s="4"/>
       <c r="C152" s="5"/>
@@ -3293,7 +3228,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="3"/>
       <c r="B153" s="4"/>
       <c r="C153" s="5"/>
@@ -3308,7 +3243,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="154" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="3"/>
       <c r="B154" s="4"/>
       <c r="C154" s="5"/>
@@ -3323,7 +3258,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="155" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="3"/>
       <c r="B155" s="4"/>
       <c r="C155" s="5"/>
@@ -3338,7 +3273,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="156" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="3"/>
       <c r="B156" s="4"/>
       <c r="C156" s="5"/>
@@ -3353,7 +3288,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="3"/>
       <c r="B157" s="4"/>
       <c r="C157" s="5"/>
@@ -3368,7 +3303,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="158" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="3"/>
       <c r="B158" s="4"/>
       <c r="C158" s="5"/>
@@ -3383,7 +3318,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="159" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="3"/>
       <c r="B159" s="4"/>
       <c r="C159" s="5"/>
@@ -3398,7 +3333,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="160" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="3"/>
       <c r="B160" s="4"/>
       <c r="C160" s="5"/>
@@ -3413,7 +3348,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="161" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="3"/>
       <c r="B161" s="4"/>
       <c r="C161" s="5"/>
@@ -3428,7 +3363,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="3"/>
       <c r="B162" s="4"/>
       <c r="C162" s="5"/>
@@ -3443,7 +3378,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="163" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="3"/>
       <c r="B163" s="4"/>
       <c r="C163" s="5"/>
@@ -3458,7 +3393,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="164" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="3"/>
       <c r="B164" s="4"/>
       <c r="C164" s="5"/>
@@ -3473,7 +3408,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="165" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="3"/>
       <c r="B165" s="4"/>
       <c r="C165" s="5"/>
@@ -3488,7 +3423,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="166" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="3"/>
       <c r="B166" s="4"/>
       <c r="C166" s="5"/>
@@ -3503,7 +3438,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="167" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="3"/>
       <c r="B167" s="4"/>
       <c r="C167" s="5"/>
@@ -3518,7 +3453,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="168" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="3"/>
       <c r="B168" s="4"/>
       <c r="C168" s="5"/>
@@ -3533,7 +3468,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="169" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="3"/>
       <c r="B169" s="4"/>
       <c r="C169" s="5"/>
@@ -3548,7 +3483,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="170" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="3"/>
       <c r="B170" s="4"/>
       <c r="C170" s="5"/>
@@ -3563,7 +3498,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="171" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="3"/>
       <c r="B171" s="4"/>
       <c r="C171" s="5"/>
@@ -3578,7 +3513,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="172" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="3"/>
       <c r="B172" s="4"/>
       <c r="C172" s="5"/>
@@ -3593,7 +3528,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="173" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="3"/>
       <c r="B173" s="4"/>
       <c r="C173" s="5"/>
@@ -3608,7 +3543,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="174" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="3"/>
       <c r="B174" s="4"/>
       <c r="C174" s="5"/>
@@ -3623,7 +3558,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="175" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="3"/>
       <c r="B175" s="4"/>
       <c r="C175" s="5"/>
@@ -3638,7 +3573,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="176" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="3"/>
       <c r="B176" s="4"/>
       <c r="C176" s="5"/>
@@ -3653,7 +3588,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="3"/>
       <c r="B177" s="4"/>
       <c r="C177" s="5"/>
@@ -3668,7 +3603,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="3"/>
       <c r="B178" s="4"/>
       <c r="C178" s="5"/>
@@ -3683,7 +3618,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="179" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="3"/>
       <c r="B179" s="4"/>
       <c r="C179" s="5"/>
@@ -3698,7 +3633,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="180" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="3"/>
       <c r="B180" s="4"/>
       <c r="C180" s="5"/>
@@ -3713,7 +3648,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="181" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="3"/>
       <c r="B181" s="4"/>
       <c r="C181" s="5"/>
@@ -3728,7 +3663,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="182" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="3"/>
       <c r="B182" s="4"/>
       <c r="C182" s="5"/>
@@ -3743,7 +3678,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="183" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="3"/>
       <c r="B183" s="4"/>
       <c r="C183" s="5"/>
@@ -3758,7 +3693,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="184" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="3"/>
       <c r="B184" s="4"/>
       <c r="C184" s="5"/>
@@ -3773,7 +3708,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="185" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="3"/>
       <c r="B185" s="4"/>
       <c r="C185" s="5"/>
@@ -3788,7 +3723,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="186" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="3"/>
       <c r="B186" s="4"/>
       <c r="C186" s="5"/>
@@ -3803,7 +3738,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="187" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="3"/>
       <c r="B187" s="4"/>
       <c r="C187" s="5"/>
@@ -3818,7 +3753,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="188" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="3"/>
       <c r="B188" s="4"/>
       <c r="C188" s="5"/>
@@ -3833,7 +3768,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="189" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="3"/>
       <c r="B189" s="4"/>
       <c r="C189" s="5"/>
@@ -3848,7 +3783,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="190" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="3"/>
       <c r="B190" s="4"/>
       <c r="C190" s="5"/>
@@ -3863,7 +3798,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="191" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="3"/>
       <c r="B191" s="4"/>
       <c r="C191" s="5"/>
@@ -3878,7 +3813,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="192" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="3"/>
       <c r="B192" s="4"/>
       <c r="C192" s="5"/>
@@ -3893,7 +3828,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="193" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="3"/>
       <c r="B193" s="4"/>
       <c r="C193" s="5"/>
@@ -3908,7 +3843,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="194" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="3"/>
       <c r="B194" s="4"/>
       <c r="C194" s="5"/>
@@ -3923,6 +3858,30 @@
         <v>#DIV/0!</v>
       </c>
     </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A195" s="11"/>
+      <c r="B195" s="11"/>
+      <c r="C195" s="11"/>
+      <c r="D195" s="11"/>
+      <c r="E195" s="11"/>
+      <c r="F195" s="11"/>
+      <c r="G195" s="11"/>
+      <c r="H195" s="11"/>
+      <c r="I195" s="11"/>
+      <c r="J195" s="11"/>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A196" s="11"/>
+      <c r="B196" s="11"/>
+      <c r="C196" s="11"/>
+      <c r="D196" s="11"/>
+      <c r="E196" s="11"/>
+      <c r="F196" s="11"/>
+      <c r="G196" s="11"/>
+      <c r="H196" s="11"/>
+      <c r="I196" s="11"/>
+      <c r="J196" s="11"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
